--- a/lottopy_site/lottopy/lottopy_web_edition/lotto.xlsx
+++ b/lottopy_site/lottopy/lottopy_web_edition/lotto.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3019"/>
+  <dimension ref="A1:G3029"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87982,6 +87982,296 @@
         </is>
       </c>
     </row>
+    <row r="3020">
+      <c r="A3020" s="1" t="n">
+        <v>3018</v>
+      </c>
+      <c r="B3020" t="inlineStr">
+        <is>
+          <t>12/22/2021</t>
+        </is>
+      </c>
+      <c r="C3020" t="inlineStr">
+        <is>
+          <t>7-16-19-48-68</t>
+        </is>
+      </c>
+      <c r="D3020" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3020" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3020" t="n">
+        <v>4413</v>
+      </c>
+      <c r="G3020" t="inlineStr">
+        <is>
+          <t>$123,861</t>
+        </is>
+      </c>
+    </row>
+    <row r="3021">
+      <c r="A3021" s="1" t="n">
+        <v>3019</v>
+      </c>
+      <c r="B3021" t="inlineStr">
+        <is>
+          <t>12/25/2021</t>
+        </is>
+      </c>
+      <c r="C3021" t="inlineStr">
+        <is>
+          <t>27-29-45-55-58</t>
+        </is>
+      </c>
+      <c r="D3021" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3021" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3021" t="n">
+        <v>7884</v>
+      </c>
+      <c r="G3021" t="inlineStr">
+        <is>
+          <t>$46,299</t>
+        </is>
+      </c>
+    </row>
+    <row r="3022">
+      <c r="A3022" s="1" t="n">
+        <v>3020</v>
+      </c>
+      <c r="B3022" t="inlineStr">
+        <is>
+          <t>12/27/2021</t>
+        </is>
+      </c>
+      <c r="C3022" t="inlineStr">
+        <is>
+          <t>36-38-45-62-64</t>
+        </is>
+      </c>
+      <c r="D3022" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3022" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3022" t="n">
+        <v>4851</v>
+      </c>
+      <c r="G3022" t="inlineStr">
+        <is>
+          <t>$25,733</t>
+        </is>
+      </c>
+    </row>
+    <row r="3023">
+      <c r="A3023" s="1" t="n">
+        <v>3021</v>
+      </c>
+      <c r="B3023" t="inlineStr">
+        <is>
+          <t>12/29/2021</t>
+        </is>
+      </c>
+      <c r="C3023" t="inlineStr">
+        <is>
+          <t>2-6-9-33-39</t>
+        </is>
+      </c>
+      <c r="D3023" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3023" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3023" t="n">
+        <v>8073</v>
+      </c>
+      <c r="G3023" t="inlineStr">
+        <is>
+          <t>$192,549</t>
+        </is>
+      </c>
+    </row>
+    <row r="3024">
+      <c r="A3024" s="1" t="n">
+        <v>3022</v>
+      </c>
+      <c r="B3024" t="inlineStr">
+        <is>
+          <t>01/01/2022</t>
+        </is>
+      </c>
+      <c r="C3024" t="inlineStr">
+        <is>
+          <t>6-12-39-48-50</t>
+        </is>
+      </c>
+      <c r="D3024" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3024" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3024" t="n">
+        <v>15004</v>
+      </c>
+      <c r="G3024" t="inlineStr">
+        <is>
+          <t>$78,416</t>
+        </is>
+      </c>
+    </row>
+    <row r="3025">
+      <c r="A3025" s="1" t="n">
+        <v>3023</v>
+      </c>
+      <c r="B3025" t="inlineStr">
+        <is>
+          <t>01/03/2022</t>
+        </is>
+      </c>
+      <c r="C3025" t="inlineStr">
+        <is>
+          <t>2-13-32-33-48</t>
+        </is>
+      </c>
+      <c r="D3025" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3025" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3025" t="n">
+        <v>9057</v>
+      </c>
+      <c r="G3025" t="inlineStr">
+        <is>
+          <t>$47,939</t>
+        </is>
+      </c>
+    </row>
+    <row r="3026">
+      <c r="A3026" s="1" t="n">
+        <v>3024</v>
+      </c>
+      <c r="B3026" t="inlineStr">
+        <is>
+          <t>01/05/2022</t>
+        </is>
+      </c>
+      <c r="C3026" t="inlineStr">
+        <is>
+          <t>6-14-25-33-46</t>
+        </is>
+      </c>
+      <c r="D3026" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3026" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3026" t="n">
+        <v>17059</v>
+      </c>
+      <c r="G3026" t="inlineStr">
+        <is>
+          <t>$136,964</t>
+        </is>
+      </c>
+    </row>
+    <row r="3027">
+      <c r="A3027" s="1" t="n">
+        <v>3025</v>
+      </c>
+      <c r="B3027" t="inlineStr">
+        <is>
+          <t>01/08/2022</t>
+        </is>
+      </c>
+      <c r="C3027" t="inlineStr">
+        <is>
+          <t>20-21-36-60-65</t>
+        </is>
+      </c>
+      <c r="D3027" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3027" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3027" t="n">
+        <v>4143</v>
+      </c>
+      <c r="G3027" t="inlineStr">
+        <is>
+          <t>$49,179</t>
+        </is>
+      </c>
+    </row>
+    <row r="3028">
+      <c r="A3028" s="1" t="n">
+        <v>3026</v>
+      </c>
+      <c r="B3028" t="inlineStr">
+        <is>
+          <t>01/10/2022</t>
+        </is>
+      </c>
+      <c r="C3028" t="inlineStr">
+        <is>
+          <t>14-17-18-21-27</t>
+        </is>
+      </c>
+      <c r="D3028" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3028" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3028" t="n">
+        <v>1968</v>
+      </c>
+      <c r="G3028" t="inlineStr">
+        <is>
+          <t>$10,941</t>
+        </is>
+      </c>
+    </row>
+    <row r="3029">
+      <c r="A3029" s="1" t="n">
+        <v>3027</v>
+      </c>
+      <c r="B3029" t="inlineStr">
+        <is>
+          <t>01/12/2022</t>
+        </is>
+      </c>
+      <c r="C3029" t="inlineStr">
+        <is>
+          <t>12-21-22-30-33</t>
+        </is>
+      </c>
+      <c r="D3029" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3029" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3029" t="n">
+        <v>2782</v>
+      </c>
+      <c r="G3029" t="inlineStr">
+        <is>
+          <t>$21,778</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lottopy_site/lottopy/lottopy_web_edition/lotto.xlsx
+++ b/lottopy_site/lottopy/lottopy_web_edition/lotto.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,26 +466,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05/21/2022</t>
+          <t>05/25/2022</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14–15–25–52–58</t>
+          <t>19–28–39–42–57</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>3589</v>
+        <v>2505</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>$19,081</t>
+          <t>$16,022</t>
         </is>
       </c>
     </row>
@@ -495,26 +495,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05/18/2022</t>
+          <t>05/23/2022</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40–41–58–64–65</t>
+          <t>1–33–37–39–42</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>2497</v>
+        <v>1861</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>$15,527</t>
+          <t>$10,215</t>
         </is>
       </c>
     </row>
@@ -524,26 +524,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05/16/2022</t>
+          <t>05/21/2022</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>7–15–22–36–64</t>
+          <t>14–15–25–52–58</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>2051</v>
+        <v>3589</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>$11,124</t>
+          <t>$19,081</t>
         </is>
       </c>
     </row>
@@ -553,26 +553,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>05/14/2022</t>
+          <t>05/18/2022</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6–40–41–45–52</t>
+          <t>40–41–58–64–65</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>3364</v>
+        <v>2497</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>$21,033</t>
+          <t>$15,527</t>
         </is>
       </c>
     </row>
@@ -582,26 +582,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05/11/2022</t>
+          <t>05/16/2022</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5–7–61–63–69</t>
+          <t>7–15–22–36–64</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>2266</v>
+        <v>2051</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>$12,461</t>
+          <t>$11,124</t>
         </is>
       </c>
     </row>
@@ -611,26 +611,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>05/09/2022</t>
+          <t>05/14/2022</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18–30–35–52–56</t>
+          <t>6–40–41–45–52</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>1660</v>
+        <v>3364</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>$8,855</t>
+          <t>$21,033</t>
         </is>
       </c>
     </row>
@@ -640,26 +640,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>05/07/2022</t>
+          <t>05/11/2022</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4–5–6–28–67</t>
+          <t>5–7–61–63–69</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>3376</v>
+        <v>2266</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>$18,445</t>
+          <t>$12,461</t>
         </is>
       </c>
     </row>
@@ -669,26 +669,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>05/04/2022</t>
+          <t>05/09/2022</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>37–39–55–63–69</t>
+          <t>18–30–35–52–56</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>2278</v>
+        <v>1660</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>$11,925</t>
+          <t>$8,855</t>
         </is>
       </c>
     </row>
@@ -698,26 +698,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>05/02/2022</t>
+          <t>05/07/2022</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>18–27–33–39–44</t>
+          <t>4–5–6–28–67</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>1662</v>
+        <v>3376</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>$15,265</t>
+          <t>$18,445</t>
         </is>
       </c>
     </row>
@@ -727,26 +727,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>04/30/2022</t>
+          <t>05/04/2022</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14–21–37–44–63</t>
+          <t>37–39–55–63–69</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>2815</v>
+        <v>2278</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>$17,825</t>
+          <t>$11,925</t>
         </is>
       </c>
     </row>
@@ -756,26 +756,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>04/27/2022</t>
+          <t>05/02/2022</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11–36–61–62–68</t>
+          <t>18–27–33–39–44</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>6965</v>
+        <v>1662</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>$35,750</t>
+          <t>$15,265</t>
         </is>
       </c>
     </row>
@@ -785,26 +785,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>04/25/2022</t>
+          <t>04/30/2022</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12–18–20–39–61</t>
+          <t>14–21–37–44–63</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>4259</v>
+        <v>2815</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$22,856</t>
+          <t>$17,825</t>
         </is>
       </c>
     </row>
@@ -814,26 +814,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>04/23/2022</t>
+          <t>04/27/2022</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10–39–47–49–56</t>
+          <t>11–36–61–62–68</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>6457</v>
+        <v>6965</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>$38,869</t>
+          <t>$35,750</t>
         </is>
       </c>
     </row>
@@ -843,26 +843,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>04/20/2022</t>
+          <t>04/25/2022</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20–30–45–55–56</t>
+          <t>12–18–20–39–61</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>3844</v>
+        <v>4259</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>$20,255</t>
+          <t>$22,856</t>
         </is>
       </c>
     </row>
@@ -872,26 +872,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>04/18/2022</t>
+          <t>04/23/2022</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>8–33–55–59–62</t>
+          <t>10–39–47–49–56</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>2688</v>
+        <v>6457</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>$14,224</t>
+          <t>$38,869</t>
         </is>
       </c>
     </row>
@@ -901,26 +901,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>04/16/2022</t>
+          <t>04/20/2022</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15–21–32–62–65</t>
+          <t>20–30–45–55–56</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>5160</v>
+        <v>3844</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>$39,825</t>
+          <t>$20,255</t>
         </is>
       </c>
     </row>
@@ -930,26 +930,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>04/13/2022</t>
+          <t>04/18/2022</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14–16–41–63–68</t>
+          <t>8–33–55–59–62</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>3741</v>
+        <v>2688</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>$19,516</t>
+          <t>$14,224</t>
         </is>
       </c>
     </row>
@@ -959,26 +959,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>04/11/2022</t>
+          <t>04/16/2022</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5–7–24–31–34</t>
+          <t>15–21–32–62–65</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>2417</v>
+        <v>5160</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>$14,052</t>
+          <t>$39,825</t>
         </is>
       </c>
     </row>
@@ -988,26 +988,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>04/09/2022</t>
+          <t>04/13/2022</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6–16–31–62–66</t>
+          <t>14–16–41–63–68</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>4503</v>
+        <v>3741</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>$23,731</t>
+          <t>$19,516</t>
         </is>
       </c>
     </row>
@@ -1017,26 +1017,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>04/06/2022</t>
+          <t>04/11/2022</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6–42–45–47–64</t>
+          <t>5–7–24–31–34</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>3310</v>
+        <v>2417</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>$20,766</t>
+          <t>$14,052</t>
         </is>
       </c>
     </row>
@@ -1046,26 +1046,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>04/04/2022</t>
+          <t>04/09/2022</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2–32–39–46–69</t>
+          <t>6–16–31–62–66</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>2330</v>
+        <v>4503</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>$62,603</t>
+          <t>$23,731</t>
         </is>
       </c>
     </row>
@@ -1075,26 +1075,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>04/02/2022</t>
+          <t>04/06/2022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6–28–47–58–59</t>
+          <t>6–42–45–47–64</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>18</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>4468</v>
+        <v>3310</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>$23,828</t>
+          <t>$20,766</t>
         </is>
       </c>
     </row>
@@ -1104,26 +1104,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>03/30/2022</t>
+          <t>04/04/2022</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3–7–21–31–37</t>
+          <t>2–32–39–46–69</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>3227</v>
+        <v>2330</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>$21,396</t>
+          <t>$62,603</t>
         </is>
       </c>
     </row>
@@ -1133,26 +1133,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>03/28/2022</t>
+          <t>04/02/2022</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>11–18–39–58–62</t>
+          <t>6–28–47–58–59</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>2106</v>
+        <v>4468</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>$11,495</t>
+          <t>$23,828</t>
         </is>
       </c>
     </row>
@@ -1162,26 +1162,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>03/26/2022</t>
+          <t>03/30/2022</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2–10–50–59–61</t>
+          <t>3–7–21–31–37</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
         <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>3931</v>
+        <v>3227</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>$24,782</t>
+          <t>$21,396</t>
         </is>
       </c>
     </row>
@@ -1191,26 +1191,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>03/23/2022</t>
+          <t>03/28/2022</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>31–32–37–38–48</t>
+          <t>11–18–39–58–62</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>2814</v>
+        <v>2106</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>$65,889</t>
+          <t>$11,495</t>
         </is>
       </c>
     </row>
@@ -1220,26 +1220,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>03/21/2022</t>
+          <t>03/26/2022</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1–15–26–63–65</t>
+          <t>2–10–50–59–61</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>1797</v>
+        <v>3931</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>$9,529</t>
+          <t>$24,782</t>
         </is>
       </c>
     </row>
@@ -1249,26 +1249,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>03/19/2022</t>
+          <t>03/23/2022</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>8–9–18–48–52</t>
+          <t>31–32–37–38–48</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>3802</v>
+        <v>2814</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>$70,218</t>
+          <t>$65,889</t>
         </is>
       </c>
     </row>
@@ -1278,26 +1278,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>03/16/2022</t>
+          <t>03/21/2022</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3–28–34–35–58</t>
+          <t>1–15–26–63–65</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>2724</v>
+        <v>1797</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>$14,515</t>
+          <t>$9,529</t>
         </is>
       </c>
     </row>
@@ -1307,26 +1307,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>03/14/2022</t>
+          <t>03/19/2022</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>21–28–32–44–49</t>
+          <t>8–9–18–48–52</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>1860</v>
+        <v>3802</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>$11,769</t>
+          <t>$70,218</t>
         </is>
       </c>
     </row>
@@ -1336,26 +1336,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>03/12/2022</t>
+          <t>03/16/2022</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19–20–37–39–61</t>
+          <t>3–28–34–35–58</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E32" t="n">
         <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>3361</v>
+        <v>2724</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>$17,986</t>
+          <t>$14,515</t>
         </is>
       </c>
     </row>
@@ -1365,26 +1365,26 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>03/09/2022</t>
+          <t>03/14/2022</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>13–22–34–51–67</t>
+          <t>21–28–32–44–49</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>2618</v>
+        <v>1860</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>$14,396</t>
+          <t>$11,769</t>
         </is>
       </c>
     </row>
@@ -1394,26 +1394,26 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>03/07/2022</t>
+          <t>03/12/2022</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10–43–55–59–67</t>
+          <t>19–20–37–39–61</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>1619</v>
+        <v>3361</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>$160,016</t>
+          <t>$17,986</t>
         </is>
       </c>
     </row>
@@ -1423,26 +1423,26 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>03/05/2022</t>
+          <t>03/09/2022</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>8–23–37–52–63</t>
+          <t>13–22–34–51–67</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>3927</v>
+        <v>2618</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>$20,702</t>
+          <t>$14,396</t>
         </is>
       </c>
     </row>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>03/02/2022</t>
+          <t>03/07/2022</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>19–37–48–61–63</t>
+          <t>10–43–55–59–67</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>2488</v>
+        <v>1619</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>$13,667</t>
+          <t>$160,016</t>
         </is>
       </c>
     </row>
@@ -1481,26 +1481,26 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>02/28/2022</t>
+          <t>03/05/2022</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>7–21–39–47–55</t>
+          <t>8–23–37–52–63</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E37" t="n">
         <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>1715</v>
+        <v>3927</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>$9,855</t>
+          <t>$20,702</t>
         </is>
       </c>
     </row>
@@ -1510,26 +1510,26 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>02/26/2022</t>
+          <t>03/02/2022</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>15–32–36–48–64</t>
+          <t>19–37–48–61–63</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>3228</v>
+        <v>2488</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>$20,406</t>
+          <t>$13,667</t>
         </is>
       </c>
     </row>
@@ -1539,26 +1539,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>02/23/2022</t>
+          <t>02/28/2022</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>6–17–21–35–64</t>
+          <t>7–21–39–47–55</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>2402</v>
+        <v>1715</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>$12,893</t>
+          <t>$9,855</t>
         </is>
       </c>
     </row>
@@ -1568,26 +1568,26 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>02/21/2022</t>
+          <t>02/26/2022</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2–36–37–45–69</t>
+          <t>15–32–36–48–64</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>1699</v>
+        <v>3228</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>$9,608</t>
+          <t>$20,406</t>
         </is>
       </c>
     </row>
@@ -1597,26 +1597,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>02/19/2022</t>
+          <t>02/23/2022</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3–10–15–33–42</t>
+          <t>6–17–21–35–64</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E41" t="n">
         <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>3430</v>
+        <v>2402</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>$18,437</t>
+          <t>$12,893</t>
         </is>
       </c>
     </row>
@@ -1626,26 +1626,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>02/16/2022</t>
+          <t>02/21/2022</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>22–30–40–42–48</t>
+          <t>2–36–37–45–69</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
         <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>2213</v>
+        <v>1699</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>$11,803</t>
+          <t>$9,608</t>
         </is>
       </c>
     </row>
@@ -1655,26 +1655,26 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>02/14/2022</t>
+          <t>02/19/2022</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>16–25–27–49–55</t>
+          <t>3–10–15–33–42</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>2080</v>
+        <v>3430</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>$63,441</t>
+          <t>$18,437</t>
         </is>
       </c>
     </row>
@@ -1684,26 +1684,26 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>02/12/2022</t>
+          <t>02/16/2022</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>8–10–21–41–62</t>
+          <t>22–30–40–42–48</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>4805</v>
+        <v>2213</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>$30,505</t>
+          <t>$11,803</t>
         </is>
       </c>
     </row>
@@ -1713,26 +1713,26 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>02/09/2022</t>
+          <t>02/14/2022</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2–17–33–51–63</t>
+          <t>16–25–27–49–55</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F45" t="n">
-        <v>3170</v>
+        <v>2080</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>$17,047</t>
+          <t>$63,441</t>
         </is>
       </c>
     </row>
@@ -1742,26 +1742,26 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>02/07/2022</t>
+          <t>02/12/2022</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5–15–38–47–65</t>
+          <t>8–10–21–41–62</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E46" t="n">
         <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>2219</v>
+        <v>4805</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>$14,620</t>
+          <t>$30,505</t>
         </is>
       </c>
     </row>
@@ -1771,26 +1771,26 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>02/05/2022</t>
+          <t>02/09/2022</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>5–16–27–39–61</t>
+          <t>2–17–33–51–63</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E47" t="n">
         <v>2</v>
       </c>
       <c r="F47" t="n">
-        <v>3910</v>
+        <v>3170</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>$70,790</t>
+          <t>$17,047</t>
         </is>
       </c>
     </row>
@@ -1800,26 +1800,26 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>02/02/2022</t>
+          <t>02/07/2022</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>18–29–33–62–63</t>
+          <t>5–15–38–47–65</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E48" t="n">
         <v>3</v>
       </c>
       <c r="F48" t="n">
-        <v>2852</v>
+        <v>2219</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>$17,682</t>
+          <t>$14,620</t>
         </is>
       </c>
     </row>
@@ -1829,26 +1829,26 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01/31/2022</t>
+          <t>02/05/2022</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>10–15–51–61–69</t>
+          <t>5–16–27–39–61</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
-        <v>1877</v>
+        <v>3910</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>$12,115</t>
+          <t>$70,790</t>
         </is>
       </c>
     </row>
@@ -1858,26 +1858,26 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01/29/2022</t>
+          <t>02/02/2022</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2–15–38–54–65</t>
+          <t>18–29–33–62–63</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>3836</v>
+        <v>2852</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>$27,233</t>
+          <t>$17,682</t>
         </is>
       </c>
     </row>
@@ -1887,26 +1887,26 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01/26/2022</t>
+          <t>01/31/2022</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>4–11–38–49–69</t>
+          <t>10–15–51–61–69</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E51" t="n">
         <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>2390</v>
+        <v>1877</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>$15,230</t>
+          <t>$12,115</t>
         </is>
       </c>
     </row>
@@ -1916,26 +1916,26 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01/24/2022</t>
+          <t>01/29/2022</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>11–29–30–47–53</t>
+          <t>2–15–38–54–65</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>1657</v>
+        <v>3836</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>$10,526</t>
+          <t>$27,233</t>
         </is>
       </c>
     </row>
@@ -1945,26 +1945,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01/22/2022</t>
+          <t>01/26/2022</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>8–14–33–36–67</t>
+          <t>4–11–38–49–69</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53" t="n">
-        <v>3412</v>
+        <v>2390</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>$17,955</t>
+          <t>$15,230</t>
         </is>
       </c>
     </row>
@@ -1974,26 +1974,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01/19/2022</t>
+          <t>01/24/2022</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>11–15–43–55–61</t>
+          <t>11–29–30–47–53</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E54" t="n">
         <v>3</v>
       </c>
       <c r="F54" t="n">
-        <v>2614</v>
+        <v>1657</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>$16,581</t>
+          <t>$10,526</t>
         </is>
       </c>
     </row>
@@ -2003,26 +2003,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01/17/2022</t>
+          <t>01/22/2022</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>9–24–35–46–65</t>
+          <t>8–14–33–36–67</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E55" t="n">
         <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>1152</v>
+        <v>3412</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>$6,245</t>
+          <t>$17,955</t>
         </is>
       </c>
     </row>
@@ -2032,26 +2032,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01/15/2022</t>
+          <t>01/19/2022</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3–18–37–51–59</t>
+          <t>11–15–43–55–61</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
-        <v>4389</v>
+        <v>2614</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>$23,619</t>
+          <t>$16,581</t>
         </is>
       </c>
     </row>
@@ -2061,26 +2061,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01/12/2022</t>
+          <t>01/17/2022</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>12–21–22–30–33</t>
+          <t>9–24–35–46–65</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
-        <v>2782</v>
+        <v>1152</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>$21,778</t>
+          <t>$6,245</t>
         </is>
       </c>
     </row>
@@ -2090,26 +2090,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/15/2022</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>14–17–18–21–27</t>
+          <t>3–18–37–51–59</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E58" t="n">
         <v>2</v>
       </c>
       <c r="F58" t="n">
-        <v>1968</v>
+        <v>4389</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>$10,941</t>
+          <t>$23,619</t>
         </is>
       </c>
     </row>
@@ -2119,26 +2119,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01/08/2022</t>
+          <t>01/12/2022</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>20–21–36–60–65</t>
+          <t>12–21–22–30–33</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E59" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F59" t="n">
-        <v>4143</v>
+        <v>2782</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>$49,179</t>
+          <t>$21,778</t>
         </is>
       </c>
     </row>
@@ -2148,26 +2148,26 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01/05/2022</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>6–14–25–33–46</t>
+          <t>14–17–18–21–27</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E60" t="n">
         <v>2</v>
       </c>
       <c r="F60" t="n">
-        <v>17059</v>
+        <v>1968</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>$136,964</t>
+          <t>$10,941</t>
         </is>
       </c>
     </row>
@@ -2177,26 +2177,26 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01/03/2022</t>
+          <t>01/08/2022</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2–13–32–33–48</t>
+          <t>20–21–36–60–65</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F61" t="n">
-        <v>9057</v>
+        <v>4143</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>$47,939</t>
+          <t>$49,179</t>
         </is>
       </c>
     </row>
@@ -2206,26 +2206,26 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/05/2022</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>6–12–39–48–50</t>
+          <t>6–14–25–33–46</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E62" t="n">
         <v>2</v>
       </c>
       <c r="F62" t="n">
-        <v>15004</v>
+        <v>17059</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>$78,416</t>
+          <t>$136,964</t>
         </is>
       </c>
     </row>
@@ -2235,26 +2235,26 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>12/29/2021</t>
+          <t>01/03/2022</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2–6–9–33–39</t>
+          <t>2–13–32–33–48</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E63" t="n">
         <v>2</v>
       </c>
       <c r="F63" t="n">
-        <v>8073</v>
+        <v>9057</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>$192,549</t>
+          <t>$47,939</t>
         </is>
       </c>
     </row>
@@ -2264,26 +2264,26 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12/27/2021</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>36–38–45–62–64</t>
+          <t>6–12–39–48–50</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E64" t="n">
         <v>2</v>
       </c>
       <c r="F64" t="n">
-        <v>4851</v>
+        <v>15004</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>$25,733</t>
+          <t>$78,416</t>
         </is>
       </c>
     </row>
@@ -2293,26 +2293,26 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12/25/2021</t>
+          <t>12/29/2021</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>27–29–45–55–58</t>
+          <t>2–6–9–33–39</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>7884</v>
+        <v>8073</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>$46,299</t>
+          <t>$192,549</t>
         </is>
       </c>
     </row>
@@ -2322,26 +2322,26 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12/22/2021</t>
+          <t>12/27/2021</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>7–16–19–48–68</t>
+          <t>36–38–45–62–64</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E66" t="n">
         <v>2</v>
       </c>
       <c r="F66" t="n">
-        <v>4413</v>
+        <v>4851</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>$123,861</t>
+          <t>$25,733</t>
         </is>
       </c>
     </row>
@@ -2351,26 +2351,26 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12/20/2021</t>
+          <t>12/25/2021</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2–13–23–34–66</t>
+          <t>27–29–45–55–58</t>
         </is>
       </c>
       <c r="D67" t="n">
         <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F67" t="n">
-        <v>2901</v>
+        <v>7884</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>$20,406</t>
+          <t>$46,299</t>
         </is>
       </c>
     </row>
@@ -2380,26 +2380,26 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12/18/2021</t>
+          <t>12/22/2021</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2–6–24–51–61</t>
+          <t>7–16–19–48–68</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E68" t="n">
         <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>5456</v>
+        <v>4413</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>$29,465</t>
+          <t>$123,861</t>
         </is>
       </c>
     </row>
@@ -2409,26 +2409,26 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12/15/2021</t>
+          <t>12/20/2021</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>19–20–40–42–59</t>
+          <t>2–13–23–34–66</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>4068</v>
+        <v>2901</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>$25,115</t>
+          <t>$20,406</t>
         </is>
       </c>
     </row>
@@ -2438,26 +2438,26 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>12/13/2021</t>
+          <t>12/18/2021</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>10–30–37–53–59</t>
+          <t>2–6–24–51–61</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
         <v>2</v>
       </c>
       <c r="F70" t="n">
-        <v>2651</v>
+        <v>5456</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>$13,704</t>
+          <t>$29,465</t>
         </is>
       </c>
     </row>
@@ -2467,26 +2467,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>12/11/2021</t>
+          <t>12/15/2021</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>3–25–44–53–64</t>
+          <t>19–20–40–42–59</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F71" t="n">
-        <v>5553</v>
+        <v>4068</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>$79,318</t>
+          <t>$25,115</t>
         </is>
       </c>
     </row>
@@ -2496,26 +2496,26 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12/08/2021</t>
+          <t>12/13/2021</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>3–7–33–50–69</t>
+          <t>10–30–37–53–59</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E72" t="n">
         <v>2</v>
       </c>
       <c r="F72" t="n">
-        <v>3721</v>
+        <v>2651</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>$19,905</t>
+          <t>$13,704</t>
         </is>
       </c>
     </row>
@@ -2525,26 +2525,26 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12/06/2021</t>
+          <t>12/11/2021</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>3–21–38–50–59</t>
+          <t>3–25–44–53–64</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
-        <v>2438</v>
+        <v>5553</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>$16,101</t>
+          <t>$79,318</t>
         </is>
       </c>
     </row>
@@ -2554,26 +2554,26 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12/04/2021</t>
+          <t>12/08/2021</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>10–40–45–56–67</t>
+          <t>3–7–33–50–69</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E74" t="n">
         <v>2</v>
       </c>
       <c r="F74" t="n">
-        <v>4459</v>
+        <v>3721</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>$23,515</t>
+          <t>$19,905</t>
         </is>
       </c>
     </row>
@@ -2583,26 +2583,26 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>12/01/2021</t>
+          <t>12/06/2021</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>12–15–38–57–63</t>
+          <t>3–21–38–50–59</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F75" t="n">
-        <v>3559</v>
+        <v>2438</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>$19,369</t>
+          <t>$16,101</t>
         </is>
       </c>
     </row>
@@ -2612,26 +2612,26 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>11/29/2021</t>
+          <t>12/04/2021</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>18–26–28–38–47</t>
+          <t>10–40–45–56–67</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
         <v>2</v>
       </c>
       <c r="F76" t="n">
-        <v>2308</v>
+        <v>4459</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>$12,206</t>
+          <t>$23,515</t>
         </is>
       </c>
     </row>
@@ -2641,26 +2641,26 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>11/27/2021</t>
+          <t>12/01/2021</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>8–32–55–64–66</t>
+          <t>12–15–38–57–63</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E77" t="n">
         <v>2</v>
       </c>
       <c r="F77" t="n">
-        <v>4202</v>
+        <v>3559</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>$22,061</t>
+          <t>$19,369</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>11/24/2021</t>
+          <t>11/29/2021</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>10–16–32–63–65</t>
+          <t>18–26–28–38–47</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -2685,11 +2685,11 @@
         <v>2</v>
       </c>
       <c r="F78" t="n">
-        <v>3443</v>
+        <v>2308</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>$18,692</t>
+          <t>$12,206</t>
         </is>
       </c>
     </row>
@@ -2699,26 +2699,26 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>11/22/2021</t>
+          <t>11/27/2021</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>7–20–29–38–67</t>
+          <t>8–32–55–64–66</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E79" t="n">
         <v>2</v>
       </c>
       <c r="F79" t="n">
-        <v>2145</v>
+        <v>4202</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>$11,570</t>
+          <t>$22,061</t>
         </is>
       </c>
     </row>
@@ -2728,26 +2728,26 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>11/20/2021</t>
+          <t>11/24/2021</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>40–43–48–59–69</t>
+          <t>10–16–32–63–65</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F80" t="n">
-        <v>4327</v>
+        <v>3443</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>$27,213</t>
+          <t>$18,692</t>
         </is>
       </c>
     </row>
@@ -2757,26 +2757,26 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>11/17/2021</t>
+          <t>11/22/2021</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>3–16–48–52–60</t>
+          <t>7–20–29–38–67</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F81" t="n">
-        <v>2671</v>
+        <v>2145</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>$16,328</t>
+          <t>$11,570</t>
         </is>
       </c>
     </row>
@@ -2786,26 +2786,26 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>11/15/2021</t>
+          <t>11/20/2021</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>5–31–34–51–53</t>
+          <t>40–43–48–59–69</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
-        <v>1980</v>
+        <v>4327</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>$10,688</t>
+          <t>$27,213</t>
         </is>
       </c>
     </row>
@@ -2815,26 +2815,26 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>11/13/2021</t>
+          <t>11/17/2021</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>8–15–26–35–45</t>
+          <t>3–16–48–52–60</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
         <v>3</v>
       </c>
       <c r="F83" t="n">
-        <v>4269</v>
+        <v>2671</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>$28,180</t>
+          <t>$16,328</t>
         </is>
       </c>
     </row>
@@ -2844,26 +2844,26 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>11/10/2021</t>
+          <t>11/15/2021</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>19–25–43–46–48</t>
+          <t>5–31–34–51–53</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E84" t="n">
         <v>2</v>
       </c>
       <c r="F84" t="n">
-        <v>2906</v>
+        <v>1980</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>$15,508</t>
+          <t>$10,688</t>
         </is>
       </c>
     </row>
@@ -2873,26 +2873,26 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>11/08/2021</t>
+          <t>11/13/2021</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>21–46–47–57–62</t>
+          <t>8–15–26–35–45</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E85" t="n">
         <v>3</v>
       </c>
       <c r="F85" t="n">
-        <v>2026</v>
+        <v>4269</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>$12,653</t>
+          <t>$28,180</t>
         </is>
       </c>
     </row>
@@ -2902,26 +2902,26 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>11/06/2021</t>
+          <t>11/10/2021</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>8–30–48–57–64</t>
+          <t>19–25–43–46–48</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E86" t="n">
         <v>2</v>
       </c>
       <c r="F86" t="n">
-        <v>4093</v>
+        <v>2906</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>$21,522</t>
+          <t>$15,508</t>
         </is>
       </c>
     </row>
@@ -2931,26 +2931,26 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>11/03/2021</t>
+          <t>11/08/2021</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1–2–24–50–57</t>
+          <t>21–46–47–57–62</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F87" t="n">
-        <v>3074</v>
+        <v>2026</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>$16,272</t>
+          <t>$12,653</t>
         </is>
       </c>
     </row>
@@ -2960,26 +2960,26 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>11/01/2021</t>
+          <t>11/06/2021</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>9–25–34–44–45</t>
+          <t>8–30–48–57–64</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F88" t="n">
-        <v>2018</v>
+        <v>4093</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>$13,357</t>
+          <t>$21,522</t>
         </is>
       </c>
     </row>
@@ -2989,26 +2989,26 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>10/30/2021</t>
+          <t>11/03/2021</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>5–23–28–43–56</t>
+          <t>1–2–24–50–57</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E89" t="n">
         <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>4041</v>
+        <v>3074</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>$21,171</t>
+          <t>$16,272</t>
         </is>
       </c>
     </row>
@@ -3018,26 +3018,26 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>10/27/2021</t>
+          <t>11/01/2021</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>3–6–26–35–51</t>
+          <t>9–25–34–44–45</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F90" t="n">
-        <v>2840</v>
+        <v>2018</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>$220,953</t>
+          <t>$13,357</t>
         </is>
       </c>
     </row>
@@ -3047,26 +3047,26 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>10/25/2021</t>
+          <t>10/30/2021</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>10–27–29–44–58</t>
+          <t>5–23–28–43–56</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E91" t="n">
         <v>2</v>
       </c>
       <c r="F91" t="n">
-        <v>1976</v>
+        <v>4041</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>$10,611</t>
+          <t>$21,171</t>
         </is>
       </c>
     </row>
@@ -3076,26 +3076,26 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>10/23/2021</t>
+          <t>10/27/2021</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>10–30–51–57–63</t>
+          <t>3–6–26–35–51</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
-        <v>3513</v>
+        <v>2840</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>$19,214</t>
+          <t>$220,953</t>
         </is>
       </c>
     </row>
@@ -3105,26 +3105,26 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>10/20/2021</t>
+          <t>10/25/2021</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>7–29–36–41–43</t>
+          <t>10–27–29–44–58</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E93" t="n">
         <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>2859</v>
+        <v>1976</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>$15,376</t>
+          <t>$10,611</t>
         </is>
       </c>
     </row>
@@ -3134,26 +3134,26 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>10/18/2021</t>
+          <t>10/23/2021</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>30–32–48–53–63</t>
+          <t>10–30–51–57–63</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E94" t="n">
         <v>2</v>
       </c>
       <c r="F94" t="n">
-        <v>1820</v>
+        <v>3513</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>$9,952</t>
+          <t>$19,214</t>
         </is>
       </c>
     </row>
@@ -3163,26 +3163,26 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>10/16/2021</t>
+          <t>10/20/2021</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>30–31–41–42–48</t>
+          <t>7–29–36–41–43</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>3640</v>
+        <v>2859</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>$22,644</t>
+          <t>$15,376</t>
         </is>
       </c>
     </row>
@@ -3192,26 +3192,26 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>10/13/2021</t>
+          <t>10/18/2021</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>23–29–47–59–60</t>
+          <t>30–32–48–53–63</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E96" t="n">
         <v>2</v>
       </c>
       <c r="F96" t="n">
-        <v>2516</v>
+        <v>1820</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>$13,378</t>
+          <t>$9,952</t>
         </is>
       </c>
     </row>
@@ -3221,26 +3221,26 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>10/11/2021</t>
+          <t>10/16/2021</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>11–20–33–39–65</t>
+          <t>30–31–41–42–48</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E97" t="n">
         <v>3</v>
       </c>
       <c r="F97" t="n">
-        <v>1868</v>
+        <v>3640</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>$11,712</t>
+          <t>$22,644</t>
         </is>
       </c>
     </row>
@@ -3250,26 +3250,26 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>10/09/2021</t>
+          <t>10/13/2021</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>12–17–30–45–62</t>
+          <t>23–29–47–59–60</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E98" t="n">
         <v>2</v>
       </c>
       <c r="F98" t="n">
-        <v>3781</v>
+        <v>2516</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>$70,136</t>
+          <t>$13,378</t>
         </is>
       </c>
     </row>
@@ -3279,26 +3279,26 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>10/06/2021</t>
+          <t>10/11/2021</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>1–17–52–58–64</t>
+          <t>11–20–33–39–65</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E99" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F99" t="n">
-        <v>2884</v>
+        <v>1868</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>$32,671</t>
+          <t>$11,712</t>
         </is>
       </c>
     </row>
@@ -3308,26 +3308,26 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>10/04/2021</t>
+          <t>10/09/2021</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>12–22–54–66–69</t>
+          <t>12–17–30–45–62</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E100" t="n">
         <v>2</v>
       </c>
       <c r="F100" t="n">
-        <v>10668</v>
+        <v>3781</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>$54,601</t>
+          <t>$70,136</t>
         </is>
       </c>
     </row>
@@ -3337,26 +3337,26 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>10/02/2021</t>
+          <t>10/06/2021</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>28–38–42–47–52</t>
+          <t>1–17–52–58–64</t>
         </is>
       </c>
       <c r="D101" t="n">
         <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F101" t="n">
-        <v>15092</v>
+        <v>2884</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>$177,689</t>
+          <t>$32,671</t>
         </is>
       </c>
     </row>
@@ -3366,26 +3366,26 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>09/29/2021</t>
+          <t>10/04/2021</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2–7–11–17–32</t>
+          <t>12–22–54–66–69</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F102" t="n">
-        <v>8770</v>
+        <v>10668</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>$54,769</t>
+          <t>$54,601</t>
         </is>
       </c>
     </row>
@@ -3395,26 +3395,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>09/27/2021</t>
+          <t>10/02/2021</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>21–22–39–44–60</t>
+          <t>28–38–42–47–52</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E103" t="n">
         <v>2</v>
       </c>
       <c r="F103" t="n">
-        <v>4965</v>
+        <v>15092</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>$26,284</t>
+          <t>$177,689</t>
         </is>
       </c>
     </row>
@@ -3424,26 +3424,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>09/25/2021</t>
+          <t>09/29/2021</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>22–23–37–62–63</t>
+          <t>2–7–11–17–32</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E104" t="n">
         <v>3</v>
       </c>
       <c r="F104" t="n">
-        <v>9325</v>
+        <v>8770</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>$55,118</t>
+          <t>$54,769</t>
         </is>
       </c>
     </row>
@@ -3453,26 +3453,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>09/22/2021</t>
+          <t>09/27/2021</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>20–40–47–55–63</t>
+          <t>21–22–39–44–60</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F105" t="n">
-        <v>6028</v>
+        <v>4965</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>$35,780</t>
+          <t>$26,284</t>
         </is>
       </c>
     </row>
@@ -3482,26 +3482,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>09/20/2021</t>
+          <t>09/25/2021</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>37–51–54–58–60</t>
+          <t>22–23–37–62–63</t>
         </is>
       </c>
       <c r="D106" t="n">
         <v>19</v>
       </c>
       <c r="E106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F106" t="n">
-        <v>3479</v>
+        <v>9325</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>$18,474</t>
+          <t>$55,118</t>
         </is>
       </c>
     </row>
@@ -3511,26 +3511,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>09/18/2021</t>
+          <t>09/22/2021</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>5–36–39–45–57</t>
+          <t>20–40–47–55–63</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F107" t="n">
-        <v>7699</v>
+        <v>6028</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>$90,232</t>
+          <t>$35,780</t>
         </is>
       </c>
     </row>
@@ -3540,26 +3540,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>09/15/2021</t>
+          <t>09/20/2021</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>1–4–18–46–62</t>
+          <t>37–51–54–58–60</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F108" t="n">
-        <v>5370</v>
+        <v>3479</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>$83,044</t>
+          <t>$18,474</t>
         </is>
       </c>
     </row>
@@ -3569,26 +3569,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>09/13/2021</t>
+          <t>09/18/2021</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>37–40–50–61–63</t>
+          <t>5–36–39–45–57</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F109" t="n">
-        <v>3109</v>
+        <v>7699</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>$19,473</t>
+          <t>$90,232</t>
         </is>
       </c>
     </row>
@@ -3598,26 +3598,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>09/11/2021</t>
+          <t>09/15/2021</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>20–31–38–40–49</t>
+          <t>1–4–18–46–62</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F110" t="n">
-        <v>6641</v>
+        <v>5370</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>$34,612</t>
+          <t>$83,044</t>
         </is>
       </c>
     </row>
@@ -3627,26 +3627,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>09/08/2021</t>
+          <t>09/13/2021</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>9–22–41–47–61</t>
+          <t>37–40–50–61–63</t>
         </is>
       </c>
       <c r="D111" t="n">
         <v>21</v>
       </c>
       <c r="E111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F111" t="n">
-        <v>4510</v>
+        <v>3109</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>$23,724</t>
+          <t>$19,473</t>
         </is>
       </c>
     </row>
@@ -3656,26 +3656,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>09/06/2021</t>
+          <t>09/11/2021</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>11–20–22–33–54</t>
+          <t>20–31–38–40–49</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E112" t="n">
         <v>2</v>
       </c>
       <c r="F112" t="n">
-        <v>2437</v>
+        <v>6641</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>$13,828</t>
+          <t>$34,612</t>
         </is>
       </c>
     </row>
@@ -3685,26 +3685,26 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>09/04/2021</t>
+          <t>09/08/2021</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>32–35–40–52–54</t>
+          <t>9–22–41–47–61</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E113" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F113" t="n">
-        <v>5486</v>
+        <v>4510</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>$40,763</t>
+          <t>$23,724</t>
         </is>
       </c>
     </row>
@@ -3714,26 +3714,26 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>09/01/2021</t>
+          <t>09/06/2021</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>10–20–29–48–51</t>
+          <t>11–20–22–33–54</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E114" t="n">
         <v>2</v>
       </c>
       <c r="F114" t="n">
-        <v>4201</v>
+        <v>2437</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>$22,236</t>
+          <t>$13,828</t>
         </is>
       </c>
     </row>
@@ -3743,26 +3743,26 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>08/30/2021</t>
+          <t>09/04/2021</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>3–15–45–51–61</t>
+          <t>32–35–40–52–54</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F115" t="n">
-        <v>2384</v>
+        <v>5486</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>$12,523</t>
+          <t>$40,763</t>
         </is>
       </c>
     </row>
@@ -3772,26 +3772,26 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>08/28/2021</t>
+          <t>09/01/2021</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>12–22–26–46–59</t>
+          <t>10–20–29–48–51</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E116" t="n">
         <v>2</v>
       </c>
       <c r="F116" t="n">
-        <v>5500</v>
+        <v>4201</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>$28,487</t>
+          <t>$22,236</t>
         </is>
       </c>
     </row>
@@ -3801,26 +3801,26 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>08/25/2021</t>
+          <t>08/30/2021</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>27–39–54–56–59</t>
+          <t>3–15–45–51–61</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F117" t="n">
-        <v>3782</v>
+        <v>2384</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>$22,540</t>
+          <t>$12,523</t>
         </is>
       </c>
     </row>
@@ -3830,26 +3830,26 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>08/23/2021</t>
+          <t>08/28/2021</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>17–36–47–60–61</t>
+          <t>12–22–26–46–59</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F118" t="n">
-        <v>1802</v>
+        <v>5500</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>$11,540</t>
+          <t>$28,487</t>
         </is>
       </c>
     </row>
@@ -3859,26 +3859,26 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>08/21/2021</t>
+          <t>08/25/2021</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>16–28–36–39–59</t>
+          <t>27–39–54–56–59</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F119" t="n">
-        <v>5049</v>
+        <v>3782</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>$1,026,295</t>
+          <t>$22,540</t>
         </is>
       </c>
     </row>
@@ -3888,26 +3888,26 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>08/18/2021</t>
+          <t>08/23/2021</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>35–36–51–55–61</t>
+          <t>17–36–47–60–61</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F120" t="n">
-        <v>4753</v>
+        <v>1802</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>$1,024,428</t>
+          <t>$11,540</t>
         </is>
       </c>
     </row>
@@ -3917,26 +3917,26 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>08/14/2021</t>
+          <t>08/21/2021</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>6–21–49–65–67</t>
+          <t>16–28–36–39–59</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E121" t="n">
         <v>2</v>
       </c>
       <c r="F121" t="n">
-        <v>4928</v>
+        <v>5049</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>$26,548</t>
+          <t>$1,026,295</t>
         </is>
       </c>
     </row>
@@ -3946,26 +3946,26 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>08/11/2021</t>
+          <t>08/18/2021</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>12–18–20–29–30</t>
+          <t>35–36–51–55–61</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F122" t="n">
-        <v>4238</v>
+        <v>4753</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>$27,758</t>
+          <t>$1,024,428</t>
         </is>
       </c>
     </row>
@@ -3975,26 +3975,26 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>08/07/2021</t>
+          <t>08/14/2021</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>7–24–36–54–60</t>
+          <t>6–21–49–65–67</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E123" t="n">
         <v>2</v>
       </c>
       <c r="F123" t="n">
-        <v>4741</v>
+        <v>4928</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>$24,513</t>
+          <t>$26,548</t>
         </is>
       </c>
     </row>
@@ -4004,26 +4004,26 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>08/04/2021</t>
+          <t>08/11/2021</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>5–21–32–36–58</t>
+          <t>12–18–20–29–30</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F124" t="n">
-        <v>3946</v>
+        <v>4238</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>$21,111</t>
+          <t>$27,758</t>
         </is>
       </c>
     </row>
@@ -4033,26 +4033,26 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>07/31/2021</t>
+          <t>08/07/2021</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>1–21–22–34–47</t>
+          <t>7–24–36–54–60</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E125" t="n">
         <v>2</v>
       </c>
       <c r="F125" t="n">
-        <v>4505</v>
+        <v>4741</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>$24,120</t>
+          <t>$24,513</t>
         </is>
       </c>
     </row>
@@ -4062,26 +4062,26 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>07/28/2021</t>
+          <t>08/04/2021</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>25–30–53–59–60</t>
+          <t>5–21–32–36–58</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F126" t="n">
-        <v>3889</v>
+        <v>3946</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>$73,912</t>
+          <t>$21,111</t>
         </is>
       </c>
     </row>
@@ -4091,26 +4091,26 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>07/24/2021</t>
+          <t>07/31/2021</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>1–4–11–59–67</t>
+          <t>1–21–22–34–47</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E127" t="n">
         <v>2</v>
       </c>
       <c r="F127" t="n">
-        <v>4261</v>
+        <v>4505</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>$24,125</t>
+          <t>$24,120</t>
         </is>
       </c>
     </row>
@@ -4120,26 +4120,26 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>07/21/2021</t>
+          <t>07/28/2021</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>27–28–44–67–68</t>
+          <t>25–30–53–59–60</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F128" t="n">
-        <v>3921</v>
+        <v>3889</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>$1,071,075</t>
+          <t>$73,912</t>
         </is>
       </c>
     </row>
@@ -4149,26 +4149,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>07/17/2021</t>
+          <t>07/24/2021</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>15–22–38–54–66</t>
+          <t>1–4–11–59–67</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E129" t="n">
         <v>2</v>
       </c>
       <c r="F129" t="n">
-        <v>4139</v>
+        <v>4261</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>$121,736</t>
+          <t>$24,125</t>
         </is>
       </c>
     </row>
@@ -4178,26 +4178,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>07/14/2021</t>
+          <t>07/21/2021</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>33–46–52–59–62</t>
+          <t>27–28–44–67–68</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E130" t="n">
         <v>2</v>
       </c>
       <c r="F130" t="n">
-        <v>3626</v>
+        <v>3921</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>$18,667</t>
+          <t>$1,071,075</t>
         </is>
       </c>
     </row>
@@ -4207,12 +4207,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>07/10/2021</t>
+          <t>07/17/2021</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>1–5–29–54–62</t>
+          <t>15–22–38–54–66</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -4222,11 +4222,11 @@
         <v>2</v>
       </c>
       <c r="F131" t="n">
-        <v>3988</v>
+        <v>4139</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>$171,952</t>
+          <t>$121,736</t>
         </is>
       </c>
     </row>
@@ -4236,26 +4236,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>07/07/2021</t>
+          <t>07/14/2021</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>8–21–30–49–57</t>
+          <t>33–46–52–59–62</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E132" t="n">
         <v>2</v>
       </c>
       <c r="F132" t="n">
-        <v>3589</v>
+        <v>3626</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>$19,961</t>
+          <t>$18,667</t>
         </is>
       </c>
     </row>
@@ -4265,26 +4265,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>07/03/2021</t>
+          <t>07/10/2021</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>26–40–41–55–65</t>
+          <t>1–5–29–54–62</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E133" t="n">
         <v>2</v>
       </c>
       <c r="F133" t="n">
-        <v>4074</v>
+        <v>3988</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>$21,576</t>
+          <t>$171,952</t>
         </is>
       </c>
     </row>
@@ -4294,26 +4294,26 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>06/30/2021</t>
+          <t>07/07/2021</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>24–29–50–65–66</t>
+          <t>8–21–30–49–57</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E134" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F134" t="n">
-        <v>3195</v>
+        <v>3589</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>$73,597</t>
+          <t>$19,961</t>
         </is>
       </c>
     </row>
@@ -4323,26 +4323,26 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>06/26/2021</t>
+          <t>07/03/2021</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>8–31–39–43–60</t>
+          <t>26–40–41–55–65</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F135" t="n">
-        <v>3541</v>
+        <v>4074</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>$22,713</t>
+          <t>$21,576</t>
         </is>
       </c>
     </row>
@@ -4352,26 +4352,26 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>06/23/2021</t>
+          <t>06/30/2021</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>13–20–40–51–63</t>
+          <t>24–29–50–65–66</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F136" t="n">
-        <v>2796</v>
+        <v>3195</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>$16,908</t>
+          <t>$73,597</t>
         </is>
       </c>
     </row>
@@ -4381,26 +4381,26 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>06/19/2021</t>
+          <t>06/26/2021</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>4–22–35–38–39</t>
+          <t>8–31–39–43–60</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F137" t="n">
-        <v>3396</v>
+        <v>3541</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>$18,109</t>
+          <t>$22,713</t>
         </is>
       </c>
     </row>
@@ -4410,26 +4410,26 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>06/16/2021</t>
+          <t>06/23/2021</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>19–29–34–44–50</t>
+          <t>13–20–40–51–63</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F138" t="n">
-        <v>3102</v>
+        <v>2796</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>$15,857</t>
+          <t>$16,908</t>
         </is>
       </c>
     </row>
@@ -4439,26 +4439,26 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>06/12/2021</t>
+          <t>06/19/2021</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>8–25–34–38–41</t>
+          <t>4–22–35–38–39</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F139" t="n">
-        <v>3386</v>
+        <v>3396</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>$21,343</t>
+          <t>$18,109</t>
         </is>
       </c>
     </row>
@@ -4468,26 +4468,26 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>06/09/2021</t>
+          <t>06/16/2021</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>19–28–46–50–54</t>
+          <t>19–29–34–44–50</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E140" t="n">
         <v>2</v>
       </c>
       <c r="F140" t="n">
-        <v>3205</v>
+        <v>3102</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>$17,283</t>
+          <t>$15,857</t>
         </is>
       </c>
     </row>
@@ -4497,26 +4497,26 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>06/05/2021</t>
+          <t>06/12/2021</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>44–52–54–64–69</t>
+          <t>8–25–34–38–41</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E141" t="n">
         <v>3</v>
       </c>
       <c r="F141" t="n">
-        <v>5295</v>
+        <v>3386</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>$32,299</t>
+          <t>$21,343</t>
         </is>
       </c>
     </row>
@@ -4526,26 +4526,26 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>06/02/2021</t>
+          <t>06/09/2021</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>6–7–11–66–67</t>
+          <t>19–28–46–50–54</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F142" t="n">
-        <v>4672</v>
+        <v>3205</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>$30,150</t>
+          <t>$17,283</t>
         </is>
       </c>
     </row>
@@ -4555,26 +4555,26 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>05/29/2021</t>
+          <t>06/05/2021</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>11–13–22–27–46</t>
+          <t>44–52–54–64–69</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F143" t="n">
-        <v>5088</v>
+        <v>5295</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>$27,508</t>
+          <t>$32,299</t>
         </is>
       </c>
     </row>
@@ -4584,26 +4584,55 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>05/26/2021</t>
+          <t>06/02/2021</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2–8–21–34–62</t>
+          <t>6–7–11–66–67</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F144" t="n">
-        <v>3993</v>
+        <v>4672</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>$21,917</t>
+          <t>$30,150</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>05/29/2021</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>11–13–22–27–46</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>20</v>
+      </c>
+      <c r="E145" t="n">
+        <v>2</v>
+      </c>
+      <c r="F145" t="n">
+        <v>5088</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>$27,508</t>
         </is>
       </c>
     </row>

--- a/lottopy_site/lottopy/lottopy_web_edition/lotto.xlsx
+++ b/lottopy_site/lottopy/lottopy_web_edition/lotto.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,26 +466,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05/25/2022</t>
+          <t>06/06/2022</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19–28–39–42–57</t>
+          <t>2–10–35–44–46</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>2505</v>
+        <v>1955</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>$16,022</t>
+          <t>$10,321</t>
         </is>
       </c>
     </row>
@@ -495,26 +495,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05/23/2022</t>
+          <t>06/04/2022</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1–33–37–39–42</t>
+          <t>14–16–36–52–60</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>1861</v>
+        <v>3519</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>$10,215</t>
+          <t>$21,345</t>
         </is>
       </c>
     </row>
@@ -524,26 +524,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05/21/2022</t>
+          <t>06/01/2022</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14–15–25–52–58</t>
+          <t>11–41–56–57–63</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>3589</v>
+        <v>2413</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>$19,081</t>
+          <t>$63,352</t>
         </is>
       </c>
     </row>
@@ -553,26 +553,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>05/18/2022</t>
+          <t>05/30/2022</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>40–41–58–64–65</t>
+          <t>27–28–51–68–69</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>2497</v>
+        <v>1634</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>$15,527</t>
+          <t>$8,412</t>
         </is>
       </c>
     </row>
@@ -582,26 +582,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05/16/2022</t>
+          <t>05/28/2022</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7–15–22–36–64</t>
+          <t>2–39–50–61–66</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>2051</v>
+        <v>3417</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>$11,124</t>
+          <t>$17,916</t>
         </is>
       </c>
     </row>
@@ -611,26 +611,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>05/14/2022</t>
+          <t>05/25/2022</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6–40–41–45–52</t>
+          <t>19–28–39–42–57</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>3364</v>
+        <v>2505</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>$21,033</t>
+          <t>$16,022</t>
         </is>
       </c>
     </row>
@@ -640,26 +640,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>05/11/2022</t>
+          <t>05/23/2022</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5–7–61–63–69</t>
+          <t>1–33–37–39–42</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>2266</v>
+        <v>1861</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>$12,461</t>
+          <t>$10,215</t>
         </is>
       </c>
     </row>
@@ -669,26 +669,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>05/09/2022</t>
+          <t>05/21/2022</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18–30–35–52–56</t>
+          <t>14–15–25–52–58</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>1660</v>
+        <v>3589</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>$8,855</t>
+          <t>$19,081</t>
         </is>
       </c>
     </row>
@@ -698,26 +698,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>05/07/2022</t>
+          <t>05/18/2022</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4–5–6–28–67</t>
+          <t>40–41–58–64–65</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>3376</v>
+        <v>2497</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>$18,445</t>
+          <t>$15,527</t>
         </is>
       </c>
     </row>
@@ -727,26 +727,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>05/04/2022</t>
+          <t>05/16/2022</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>37–39–55–63–69</t>
+          <t>7–15–22–36–64</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>2278</v>
+        <v>2051</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>$11,925</t>
+          <t>$11,124</t>
         </is>
       </c>
     </row>
@@ -756,26 +756,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>05/02/2022</t>
+          <t>05/14/2022</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>18–27–33–39–44</t>
+          <t>6–40–41–45–52</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>1662</v>
+        <v>3364</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>$15,265</t>
+          <t>$21,033</t>
         </is>
       </c>
     </row>
@@ -785,26 +785,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>04/30/2022</t>
+          <t>05/11/2022</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14–21–37–44–63</t>
+          <t>5–7–61–63–69</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>2815</v>
+        <v>2266</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$17,825</t>
+          <t>$12,461</t>
         </is>
       </c>
     </row>
@@ -814,26 +814,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>04/27/2022</t>
+          <t>05/09/2022</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11–36–61–62–68</t>
+          <t>18–30–35–52–56</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>6965</v>
+        <v>1660</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>$35,750</t>
+          <t>$8,855</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>04/25/2022</t>
+          <t>05/07/2022</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>12–18–20–39–61</t>
+          <t>4–5–6–28–67</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -858,11 +858,11 @@
         <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>4259</v>
+        <v>3376</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>$22,856</t>
+          <t>$18,445</t>
         </is>
       </c>
     </row>
@@ -872,26 +872,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>04/23/2022</t>
+          <t>05/04/2022</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10–39–47–49–56</t>
+          <t>37–39–55–63–69</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>6457</v>
+        <v>2278</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>$38,869</t>
+          <t>$11,925</t>
         </is>
       </c>
     </row>
@@ -901,26 +901,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>04/20/2022</t>
+          <t>05/02/2022</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20–30–45–55–56</t>
+          <t>18–27–33–39–44</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>3844</v>
+        <v>1662</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>$20,255</t>
+          <t>$15,265</t>
         </is>
       </c>
     </row>
@@ -930,26 +930,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>04/18/2022</t>
+          <t>04/30/2022</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>8–33–55–59–62</t>
+          <t>14–21–37–44–63</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>2688</v>
+        <v>2815</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>$14,224</t>
+          <t>$17,825</t>
         </is>
       </c>
     </row>
@@ -959,26 +959,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>04/16/2022</t>
+          <t>04/27/2022</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15–21–32–62–65</t>
+          <t>11–36–61–62–68</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>5160</v>
+        <v>6965</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>$39,825</t>
+          <t>$35,750</t>
         </is>
       </c>
     </row>
@@ -988,26 +988,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>04/13/2022</t>
+          <t>04/25/2022</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14–16–41–63–68</t>
+          <t>12–18–20–39–61</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>3741</v>
+        <v>4259</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>$19,516</t>
+          <t>$22,856</t>
         </is>
       </c>
     </row>
@@ -1017,26 +1017,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>04/11/2022</t>
+          <t>04/23/2022</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5–7–24–31–34</t>
+          <t>10–39–47–49–56</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>2417</v>
+        <v>6457</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>$14,052</t>
+          <t>$38,869</t>
         </is>
       </c>
     </row>
@@ -1046,26 +1046,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>04/09/2022</t>
+          <t>04/20/2022</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>6–16–31–62–66</t>
+          <t>20–30–45–55–56</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>4503</v>
+        <v>3844</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>$23,731</t>
+          <t>$20,255</t>
         </is>
       </c>
     </row>
@@ -1075,26 +1075,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>04/06/2022</t>
+          <t>04/18/2022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6–42–45–47–64</t>
+          <t>8–33–55–59–62</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>18</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>3310</v>
+        <v>2688</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>$20,766</t>
+          <t>$14,224</t>
         </is>
       </c>
     </row>
@@ -1104,26 +1104,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>04/04/2022</t>
+          <t>04/16/2022</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2–32–39–46–69</t>
+          <t>15–21–32–62–65</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>2330</v>
+        <v>5160</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>$62,603</t>
+          <t>$39,825</t>
         </is>
       </c>
     </row>
@@ -1133,26 +1133,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>04/02/2022</t>
+          <t>04/13/2022</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6–28–47–58–59</t>
+          <t>14–16–41–63–68</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>4468</v>
+        <v>3741</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>$23,828</t>
+          <t>$19,516</t>
         </is>
       </c>
     </row>
@@ -1162,26 +1162,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>03/30/2022</t>
+          <t>04/11/2022</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3–7–21–31–37</t>
+          <t>5–7–24–31–34</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>3227</v>
+        <v>2417</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>$21,396</t>
+          <t>$14,052</t>
         </is>
       </c>
     </row>
@@ -1191,26 +1191,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>03/28/2022</t>
+          <t>04/09/2022</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>11–18–39–58–62</t>
+          <t>6–16–31–62–66</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>2106</v>
+        <v>4503</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>$11,495</t>
+          <t>$23,731</t>
         </is>
       </c>
     </row>
@@ -1220,26 +1220,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>03/26/2022</t>
+          <t>04/06/2022</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2–10–50–59–61</t>
+          <t>6–42–45–47–64</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E28" t="n">
         <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>3931</v>
+        <v>3310</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>$24,782</t>
+          <t>$20,766</t>
         </is>
       </c>
     </row>
@@ -1249,26 +1249,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>03/23/2022</t>
+          <t>04/04/2022</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>31–32–37–38–48</t>
+          <t>2–32–39–46–69</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>2814</v>
+        <v>2330</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>$65,889</t>
+          <t>$62,603</t>
         </is>
       </c>
     </row>
@@ -1278,26 +1278,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>03/21/2022</t>
+          <t>04/02/2022</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1–15–26–63–65</t>
+          <t>6–28–47–58–59</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>1797</v>
+        <v>4468</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>$9,529</t>
+          <t>$23,828</t>
         </is>
       </c>
     </row>
@@ -1307,26 +1307,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>03/19/2022</t>
+          <t>03/30/2022</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>8–9–18–48–52</t>
+          <t>3–7–21–31–37</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>3802</v>
+        <v>3227</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>$70,218</t>
+          <t>$21,396</t>
         </is>
       </c>
     </row>
@@ -1336,26 +1336,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>03/16/2022</t>
+          <t>03/28/2022</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3–28–34–35–58</t>
+          <t>11–18–39–58–62</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
         <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>2724</v>
+        <v>2106</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>$14,515</t>
+          <t>$11,495</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>03/14/2022</t>
+          <t>03/26/2022</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>21–28–32–44–49</t>
+          <t>2–10–50–59–61</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1380,11 +1380,11 @@
         <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>1860</v>
+        <v>3931</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>$11,769</t>
+          <t>$24,782</t>
         </is>
       </c>
     </row>
@@ -1394,26 +1394,26 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>03/12/2022</t>
+          <t>03/23/2022</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>19–20–37–39–61</t>
+          <t>31–32–37–38–48</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E34" t="n">
         <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>3361</v>
+        <v>2814</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>$17,986</t>
+          <t>$65,889</t>
         </is>
       </c>
     </row>
@@ -1423,26 +1423,26 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>03/09/2022</t>
+          <t>03/21/2022</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>13–22–34–51–67</t>
+          <t>1–15–26–63–65</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>2618</v>
+        <v>1797</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>$14,396</t>
+          <t>$9,529</t>
         </is>
       </c>
     </row>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>03/07/2022</t>
+          <t>03/19/2022</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>10–43–55–59–67</t>
+          <t>8–9–18–48–52</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>1619</v>
+        <v>3802</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>$160,016</t>
+          <t>$70,218</t>
         </is>
       </c>
     </row>
@@ -1481,26 +1481,26 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>03/05/2022</t>
+          <t>03/16/2022</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>8–23–37–52–63</t>
+          <t>3–28–34–35–58</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E37" t="n">
         <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>3927</v>
+        <v>2724</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>$20,702</t>
+          <t>$14,515</t>
         </is>
       </c>
     </row>
@@ -1510,26 +1510,26 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>03/02/2022</t>
+          <t>03/14/2022</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>19–37–48–61–63</t>
+          <t>21–28–32–44–49</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>2488</v>
+        <v>1860</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>$13,667</t>
+          <t>$11,769</t>
         </is>
       </c>
     </row>
@@ -1539,26 +1539,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>02/28/2022</t>
+          <t>03/12/2022</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>7–21–39–47–55</t>
+          <t>19–20–37–39–61</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>1715</v>
+        <v>3361</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>$9,855</t>
+          <t>$17,986</t>
         </is>
       </c>
     </row>
@@ -1568,26 +1568,26 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>02/26/2022</t>
+          <t>03/09/2022</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>15–32–36–48–64</t>
+          <t>13–22–34–51–67</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>3228</v>
+        <v>2618</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>$20,406</t>
+          <t>$14,396</t>
         </is>
       </c>
     </row>
@@ -1597,26 +1597,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>02/23/2022</t>
+          <t>03/07/2022</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>6–17–21–35–64</t>
+          <t>10–43–55–59–67</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>2402</v>
+        <v>1619</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>$12,893</t>
+          <t>$160,016</t>
         </is>
       </c>
     </row>
@@ -1626,26 +1626,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>02/21/2022</t>
+          <t>03/05/2022</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2–36–37–45–69</t>
+          <t>8–23–37–52–63</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E42" t="n">
         <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>1699</v>
+        <v>3927</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>$9,608</t>
+          <t>$20,702</t>
         </is>
       </c>
     </row>
@@ -1655,26 +1655,26 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>02/19/2022</t>
+          <t>03/02/2022</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3–10–15–33–42</t>
+          <t>19–37–48–61–63</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E43" t="n">
         <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>3430</v>
+        <v>2488</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>$18,437</t>
+          <t>$13,667</t>
         </is>
       </c>
     </row>
@@ -1684,26 +1684,26 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>02/16/2022</t>
+          <t>02/28/2022</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>22–30–40–42–48</t>
+          <t>7–21–39–47–55</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E44" t="n">
         <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>2213</v>
+        <v>1715</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>$11,803</t>
+          <t>$9,855</t>
         </is>
       </c>
     </row>
@@ -1713,26 +1713,26 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>02/14/2022</t>
+          <t>02/26/2022</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>16–25–27–49–55</t>
+          <t>15–32–36–48–64</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E45" t="n">
         <v>3</v>
       </c>
       <c r="F45" t="n">
-        <v>2080</v>
+        <v>3228</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>$63,441</t>
+          <t>$20,406</t>
         </is>
       </c>
     </row>
@@ -1742,26 +1742,26 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>02/12/2022</t>
+          <t>02/23/2022</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>8–10–21–41–62</t>
+          <t>6–17–21–35–64</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
-        <v>4805</v>
+        <v>2402</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>$30,505</t>
+          <t>$12,893</t>
         </is>
       </c>
     </row>
@@ -1771,26 +1771,26 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>02/09/2022</t>
+          <t>02/21/2022</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2–17–33–51–63</t>
+          <t>2–36–37–45–69</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
         <v>2</v>
       </c>
       <c r="F47" t="n">
-        <v>3170</v>
+        <v>1699</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>$17,047</t>
+          <t>$9,608</t>
         </is>
       </c>
     </row>
@@ -1800,26 +1800,26 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>02/07/2022</t>
+          <t>02/19/2022</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>5–15–38–47–65</t>
+          <t>3–10–15–33–42</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F48" t="n">
-        <v>2219</v>
+        <v>3430</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>$14,620</t>
+          <t>$18,437</t>
         </is>
       </c>
     </row>
@@ -1829,26 +1829,26 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>02/05/2022</t>
+          <t>02/16/2022</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>5–16–27–39–61</t>
+          <t>22–30–40–42–48</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E49" t="n">
         <v>2</v>
       </c>
       <c r="F49" t="n">
-        <v>3910</v>
+        <v>2213</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>$70,790</t>
+          <t>$11,803</t>
         </is>
       </c>
     </row>
@@ -1858,26 +1858,26 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>02/02/2022</t>
+          <t>02/14/2022</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>18–29–33–62–63</t>
+          <t>16–25–27–49–55</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E50" t="n">
         <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>2852</v>
+        <v>2080</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>$17,682</t>
+          <t>$63,441</t>
         </is>
       </c>
     </row>
@@ -1887,26 +1887,26 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01/31/2022</t>
+          <t>02/12/2022</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>10–15–51–61–69</t>
+          <t>8–10–21–41–62</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E51" t="n">
         <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>1877</v>
+        <v>4805</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>$12,115</t>
+          <t>$30,505</t>
         </is>
       </c>
     </row>
@@ -1916,26 +1916,26 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01/29/2022</t>
+          <t>02/09/2022</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2–15–38–54–65</t>
+          <t>2–17–33–51–63</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>3836</v>
+        <v>3170</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>$27,233</t>
+          <t>$17,047</t>
         </is>
       </c>
     </row>
@@ -1945,26 +1945,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01/26/2022</t>
+          <t>02/07/2022</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>4–11–38–49–69</t>
+          <t>5–15–38–47–65</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E53" t="n">
         <v>3</v>
       </c>
       <c r="F53" t="n">
-        <v>2390</v>
+        <v>2219</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>$15,230</t>
+          <t>$14,620</t>
         </is>
       </c>
     </row>
@@ -1974,26 +1974,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01/24/2022</t>
+          <t>02/05/2022</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>11–29–30–47–53</t>
+          <t>5–16–27–39–61</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F54" t="n">
-        <v>1657</v>
+        <v>3910</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>$10,526</t>
+          <t>$70,790</t>
         </is>
       </c>
     </row>
@@ -2003,26 +2003,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01/22/2022</t>
+          <t>02/02/2022</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>8–14–33–36–67</t>
+          <t>18–29–33–62–63</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
-        <v>3412</v>
+        <v>2852</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>$17,955</t>
+          <t>$17,682</t>
         </is>
       </c>
     </row>
@@ -2032,26 +2032,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01/19/2022</t>
+          <t>01/31/2022</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>11–15–43–55–61</t>
+          <t>10–15–51–61–69</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E56" t="n">
         <v>3</v>
       </c>
       <c r="F56" t="n">
-        <v>2614</v>
+        <v>1877</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>$16,581</t>
+          <t>$12,115</t>
         </is>
       </c>
     </row>
@@ -2061,26 +2061,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01/17/2022</t>
+          <t>01/29/2022</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9–24–35–46–65</t>
+          <t>2–15–38–54–65</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F57" t="n">
-        <v>1152</v>
+        <v>3836</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>$6,245</t>
+          <t>$27,233</t>
         </is>
       </c>
     </row>
@@ -2090,26 +2090,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01/15/2022</t>
+          <t>01/26/2022</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>3–18–37–51–59</t>
+          <t>4–11–38–49–69</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F58" t="n">
-        <v>4389</v>
+        <v>2390</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>$23,619</t>
+          <t>$15,230</t>
         </is>
       </c>
     </row>
@@ -2119,26 +2119,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01/12/2022</t>
+          <t>01/24/2022</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>12–21–22–30–33</t>
+          <t>11–29–30–47–53</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F59" t="n">
-        <v>2782</v>
+        <v>1657</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>$21,778</t>
+          <t>$10,526</t>
         </is>
       </c>
     </row>
@@ -2148,26 +2148,26 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/22/2022</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>14–17–18–21–27</t>
+          <t>8–14–33–36–67</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E60" t="n">
         <v>2</v>
       </c>
       <c r="F60" t="n">
-        <v>1968</v>
+        <v>3412</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>$10,941</t>
+          <t>$17,955</t>
         </is>
       </c>
     </row>
@@ -2177,26 +2177,26 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01/08/2022</t>
+          <t>01/19/2022</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>20–21–36–60–65</t>
+          <t>11–15–43–55–61</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E61" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F61" t="n">
-        <v>4143</v>
+        <v>2614</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>$49,179</t>
+          <t>$16,581</t>
         </is>
       </c>
     </row>
@@ -2206,26 +2206,26 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01/05/2022</t>
+          <t>01/17/2022</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>6–14–25–33–46</t>
+          <t>9–24–35–46–65</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E62" t="n">
         <v>2</v>
       </c>
       <c r="F62" t="n">
-        <v>17059</v>
+        <v>1152</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>$136,964</t>
+          <t>$6,245</t>
         </is>
       </c>
     </row>
@@ -2235,26 +2235,26 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01/03/2022</t>
+          <t>01/15/2022</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2–13–32–33–48</t>
+          <t>3–18–37–51–59</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E63" t="n">
         <v>2</v>
       </c>
       <c r="F63" t="n">
-        <v>9057</v>
+        <v>4389</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>$47,939</t>
+          <t>$23,619</t>
         </is>
       </c>
     </row>
@@ -2264,26 +2264,26 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/12/2022</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>6–12–39–48–50</t>
+          <t>12–21–22–30–33</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
-        <v>15004</v>
+        <v>2782</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>$78,416</t>
+          <t>$21,778</t>
         </is>
       </c>
     </row>
@@ -2293,26 +2293,26 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12/29/2021</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2–6–9–33–39</t>
+          <t>14–17–18–21–27</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E65" t="n">
         <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>8073</v>
+        <v>1968</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>$192,549</t>
+          <t>$10,941</t>
         </is>
       </c>
     </row>
@@ -2322,26 +2322,26 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12/27/2021</t>
+          <t>01/08/2022</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>36–38–45–62–64</t>
+          <t>20–21–36–60–65</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E66" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F66" t="n">
-        <v>4851</v>
+        <v>4143</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>$25,733</t>
+          <t>$49,179</t>
         </is>
       </c>
     </row>
@@ -2351,26 +2351,26 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12/25/2021</t>
+          <t>01/05/2022</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>27–29–45–55–58</t>
+          <t>6–14–25–33–46</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
-        <v>7884</v>
+        <v>17059</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>$46,299</t>
+          <t>$136,964</t>
         </is>
       </c>
     </row>
@@ -2380,26 +2380,26 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12/22/2021</t>
+          <t>01/03/2022</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>7–16–19–48–68</t>
+          <t>2–13–32–33–48</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E68" t="n">
         <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>4413</v>
+        <v>9057</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>$123,861</t>
+          <t>$47,939</t>
         </is>
       </c>
     </row>
@@ -2409,26 +2409,26 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12/20/2021</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2–13–23–34–66</t>
+          <t>6–12–39–48–50</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
-        <v>2901</v>
+        <v>15004</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>$20,406</t>
+          <t>$78,416</t>
         </is>
       </c>
     </row>
@@ -2438,26 +2438,26 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>12/18/2021</t>
+          <t>12/29/2021</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2–6–24–51–61</t>
+          <t>2–6–9–33–39</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E70" t="n">
         <v>2</v>
       </c>
       <c r="F70" t="n">
-        <v>5456</v>
+        <v>8073</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>$29,465</t>
+          <t>$192,549</t>
         </is>
       </c>
     </row>
@@ -2467,26 +2467,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>12/15/2021</t>
+          <t>12/27/2021</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>19–20–40–42–59</t>
+          <t>36–38–45–62–64</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
-        <v>4068</v>
+        <v>4851</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>$25,115</t>
+          <t>$25,733</t>
         </is>
       </c>
     </row>
@@ -2496,26 +2496,26 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12/13/2021</t>
+          <t>12/25/2021</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>10–30–37–53–59</t>
+          <t>27–29–45–55–58</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F72" t="n">
-        <v>2651</v>
+        <v>7884</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>$13,704</t>
+          <t>$46,299</t>
         </is>
       </c>
     </row>
@@ -2525,26 +2525,26 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12/11/2021</t>
+          <t>12/22/2021</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>3–25–44–53–64</t>
+          <t>7–16–19–48–68</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E73" t="n">
         <v>2</v>
       </c>
       <c r="F73" t="n">
-        <v>5553</v>
+        <v>4413</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>$79,318</t>
+          <t>$123,861</t>
         </is>
       </c>
     </row>
@@ -2554,26 +2554,26 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12/08/2021</t>
+          <t>12/20/2021</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>3–7–33–50–69</t>
+          <t>2–13–23–34–66</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F74" t="n">
-        <v>3721</v>
+        <v>2901</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>$19,905</t>
+          <t>$20,406</t>
         </is>
       </c>
     </row>
@@ -2583,26 +2583,26 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>12/06/2021</t>
+          <t>12/18/2021</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>3–21–38–50–59</t>
+          <t>2–6–24–51–61</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F75" t="n">
-        <v>2438</v>
+        <v>5456</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>$16,101</t>
+          <t>$29,465</t>
         </is>
       </c>
     </row>
@@ -2612,26 +2612,26 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>12/04/2021</t>
+          <t>12/15/2021</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>10–40–45–56–67</t>
+          <t>19–20–40–42–59</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76" t="n">
-        <v>4459</v>
+        <v>4068</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>$23,515</t>
+          <t>$25,115</t>
         </is>
       </c>
     </row>
@@ -2641,26 +2641,26 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>12/01/2021</t>
+          <t>12/13/2021</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>12–15–38–57–63</t>
+          <t>10–30–37–53–59</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E77" t="n">
         <v>2</v>
       </c>
       <c r="F77" t="n">
-        <v>3559</v>
+        <v>2651</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>$19,369</t>
+          <t>$13,704</t>
         </is>
       </c>
     </row>
@@ -2670,26 +2670,26 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>11/29/2021</t>
+          <t>12/11/2021</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>18–26–28–38–47</t>
+          <t>3–25–44–53–64</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E78" t="n">
         <v>2</v>
       </c>
       <c r="F78" t="n">
-        <v>2308</v>
+        <v>5553</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>$12,206</t>
+          <t>$79,318</t>
         </is>
       </c>
     </row>
@@ -2699,26 +2699,26 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>11/27/2021</t>
+          <t>12/08/2021</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>8–32–55–64–66</t>
+          <t>3–7–33–50–69</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E79" t="n">
         <v>2</v>
       </c>
       <c r="F79" t="n">
-        <v>4202</v>
+        <v>3721</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>$22,061</t>
+          <t>$19,905</t>
         </is>
       </c>
     </row>
@@ -2728,26 +2728,26 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>11/24/2021</t>
+          <t>12/06/2021</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>10–16–32–63–65</t>
+          <t>3–21–38–50–59</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F80" t="n">
-        <v>3443</v>
+        <v>2438</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>$18,692</t>
+          <t>$16,101</t>
         </is>
       </c>
     </row>
@@ -2757,26 +2757,26 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>11/22/2021</t>
+          <t>12/04/2021</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>7–20–29–38–67</t>
+          <t>10–40–45–56–67</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E81" t="n">
         <v>2</v>
       </c>
       <c r="F81" t="n">
-        <v>2145</v>
+        <v>4459</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>$11,570</t>
+          <t>$23,515</t>
         </is>
       </c>
     </row>
@@ -2786,26 +2786,26 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>11/20/2021</t>
+          <t>12/01/2021</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>40–43–48–59–69</t>
+          <t>12–15–38–57–63</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
-        <v>4327</v>
+        <v>3559</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>$27,213</t>
+          <t>$19,369</t>
         </is>
       </c>
     </row>
@@ -2815,26 +2815,26 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>11/17/2021</t>
+          <t>11/29/2021</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>3–16–48–52–60</t>
+          <t>18–26–28–38–47</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F83" t="n">
-        <v>2671</v>
+        <v>2308</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>$16,328</t>
+          <t>$12,206</t>
         </is>
       </c>
     </row>
@@ -2844,26 +2844,26 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>11/15/2021</t>
+          <t>11/27/2021</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>5–31–34–51–53</t>
+          <t>8–32–55–64–66</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E84" t="n">
         <v>2</v>
       </c>
       <c r="F84" t="n">
-        <v>1980</v>
+        <v>4202</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>$10,688</t>
+          <t>$22,061</t>
         </is>
       </c>
     </row>
@@ -2873,26 +2873,26 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>11/13/2021</t>
+          <t>11/24/2021</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>8–15–26–35–45</t>
+          <t>10–16–32–63–65</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F85" t="n">
-        <v>4269</v>
+        <v>3443</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>$28,180</t>
+          <t>$18,692</t>
         </is>
       </c>
     </row>
@@ -2902,26 +2902,26 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>11/10/2021</t>
+          <t>11/22/2021</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>19–25–43–46–48</t>
+          <t>7–20–29–38–67</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E86" t="n">
         <v>2</v>
       </c>
       <c r="F86" t="n">
-        <v>2906</v>
+        <v>2145</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>$15,508</t>
+          <t>$11,570</t>
         </is>
       </c>
     </row>
@@ -2931,26 +2931,26 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>11/08/2021</t>
+          <t>11/20/2021</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>21–46–47–57–62</t>
+          <t>40–43–48–59–69</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E87" t="n">
         <v>3</v>
       </c>
       <c r="F87" t="n">
-        <v>2026</v>
+        <v>4327</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>$12,653</t>
+          <t>$27,213</t>
         </is>
       </c>
     </row>
@@ -2960,26 +2960,26 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>11/06/2021</t>
+          <t>11/17/2021</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>8–30–48–57–64</t>
+          <t>3–16–48–52–60</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
-        <v>4093</v>
+        <v>2671</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>$21,522</t>
+          <t>$16,328</t>
         </is>
       </c>
     </row>
@@ -2989,26 +2989,26 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>11/03/2021</t>
+          <t>11/15/2021</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1–2–24–50–57</t>
+          <t>5–31–34–51–53</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E89" t="n">
         <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>3074</v>
+        <v>1980</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>$16,272</t>
+          <t>$10,688</t>
         </is>
       </c>
     </row>
@@ -3018,26 +3018,26 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>11/01/2021</t>
+          <t>11/13/2021</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>9–25–34–44–45</t>
+          <t>8–15–26–35–45</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E90" t="n">
         <v>3</v>
       </c>
       <c r="F90" t="n">
-        <v>2018</v>
+        <v>4269</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>$13,357</t>
+          <t>$28,180</t>
         </is>
       </c>
     </row>
@@ -3047,26 +3047,26 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>10/30/2021</t>
+          <t>11/10/2021</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>5–23–28–43–56</t>
+          <t>19–25–43–46–48</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E91" t="n">
         <v>2</v>
       </c>
       <c r="F91" t="n">
-        <v>4041</v>
+        <v>2906</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>$21,171</t>
+          <t>$15,508</t>
         </is>
       </c>
     </row>
@@ -3076,26 +3076,26 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>10/27/2021</t>
+          <t>11/08/2021</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>3–6–26–35–51</t>
+          <t>21–46–47–57–62</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
-        <v>2840</v>
+        <v>2026</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>$220,953</t>
+          <t>$12,653</t>
         </is>
       </c>
     </row>
@@ -3105,26 +3105,26 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>10/25/2021</t>
+          <t>11/06/2021</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>10–27–29–44–58</t>
+          <t>8–30–48–57–64</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E93" t="n">
         <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>1976</v>
+        <v>4093</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>$10,611</t>
+          <t>$21,522</t>
         </is>
       </c>
     </row>
@@ -3134,26 +3134,26 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>10/23/2021</t>
+          <t>11/03/2021</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>10–30–51–57–63</t>
+          <t>1–2–24–50–57</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E94" t="n">
         <v>2</v>
       </c>
       <c r="F94" t="n">
-        <v>3513</v>
+        <v>3074</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>$19,214</t>
+          <t>$16,272</t>
         </is>
       </c>
     </row>
@@ -3163,26 +3163,26 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>10/20/2021</t>
+          <t>11/01/2021</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>7–29–36–41–43</t>
+          <t>9–25–34–44–45</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F95" t="n">
-        <v>2859</v>
+        <v>2018</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>$15,376</t>
+          <t>$13,357</t>
         </is>
       </c>
     </row>
@@ -3192,26 +3192,26 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>10/18/2021</t>
+          <t>10/30/2021</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>30–32–48–53–63</t>
+          <t>5–23–28–43–56</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E96" t="n">
         <v>2</v>
       </c>
       <c r="F96" t="n">
-        <v>1820</v>
+        <v>4041</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>$9,952</t>
+          <t>$21,171</t>
         </is>
       </c>
     </row>
@@ -3221,26 +3221,26 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>10/16/2021</t>
+          <t>10/27/2021</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>30–31–41–42–48</t>
+          <t>3–6–26–35–51</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F97" t="n">
-        <v>3640</v>
+        <v>2840</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>$22,644</t>
+          <t>$220,953</t>
         </is>
       </c>
     </row>
@@ -3250,26 +3250,26 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>10/13/2021</t>
+          <t>10/25/2021</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>23–29–47–59–60</t>
+          <t>10–27–29–44–58</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E98" t="n">
         <v>2</v>
       </c>
       <c r="F98" t="n">
-        <v>2516</v>
+        <v>1976</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>$13,378</t>
+          <t>$10,611</t>
         </is>
       </c>
     </row>
@@ -3279,26 +3279,26 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>10/11/2021</t>
+          <t>10/23/2021</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>11–20–33–39–65</t>
+          <t>10–30–51–57–63</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F99" t="n">
-        <v>1868</v>
+        <v>3513</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>$11,712</t>
+          <t>$19,214</t>
         </is>
       </c>
     </row>
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>10/09/2021</t>
+          <t>10/20/2021</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>12–17–30–45–62</t>
+          <t>7–29–36–41–43</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3323,11 +3323,11 @@
         <v>2</v>
       </c>
       <c r="F100" t="n">
-        <v>3781</v>
+        <v>2859</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>$70,136</t>
+          <t>$15,376</t>
         </is>
       </c>
     </row>
@@ -3337,26 +3337,26 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>10/06/2021</t>
+          <t>10/18/2021</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1–17–52–58–64</t>
+          <t>30–32–48–53–63</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E101" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F101" t="n">
-        <v>2884</v>
+        <v>1820</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>$32,671</t>
+          <t>$9,952</t>
         </is>
       </c>
     </row>
@@ -3366,26 +3366,26 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>10/04/2021</t>
+          <t>10/16/2021</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>12–22–54–66–69</t>
+          <t>30–31–41–42–48</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F102" t="n">
-        <v>10668</v>
+        <v>3640</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>$54,601</t>
+          <t>$22,644</t>
         </is>
       </c>
     </row>
@@ -3395,26 +3395,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>10/02/2021</t>
+          <t>10/13/2021</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>28–38–42–47–52</t>
+          <t>23–29–47–59–60</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E103" t="n">
         <v>2</v>
       </c>
       <c r="F103" t="n">
-        <v>15092</v>
+        <v>2516</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>$177,689</t>
+          <t>$13,378</t>
         </is>
       </c>
     </row>
@@ -3424,26 +3424,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>09/29/2021</t>
+          <t>10/11/2021</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2–7–11–17–32</t>
+          <t>11–20–33–39–65</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E104" t="n">
         <v>3</v>
       </c>
       <c r="F104" t="n">
-        <v>8770</v>
+        <v>1868</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>$54,769</t>
+          <t>$11,712</t>
         </is>
       </c>
     </row>
@@ -3453,26 +3453,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>09/27/2021</t>
+          <t>10/09/2021</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>21–22–39–44–60</t>
+          <t>12–17–30–45–62</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E105" t="n">
         <v>2</v>
       </c>
       <c r="F105" t="n">
-        <v>4965</v>
+        <v>3781</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>$26,284</t>
+          <t>$70,136</t>
         </is>
       </c>
     </row>
@@ -3482,26 +3482,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>09/25/2021</t>
+          <t>10/06/2021</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>22–23–37–62–63</t>
+          <t>1–17–52–58–64</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F106" t="n">
-        <v>9325</v>
+        <v>2884</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>$55,118</t>
+          <t>$32,671</t>
         </is>
       </c>
     </row>
@@ -3511,26 +3511,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>09/22/2021</t>
+          <t>10/04/2021</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>20–40–47–55–63</t>
+          <t>12–22–54–66–69</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F107" t="n">
-        <v>6028</v>
+        <v>10668</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>$35,780</t>
+          <t>$54,601</t>
         </is>
       </c>
     </row>
@@ -3540,26 +3540,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>09/20/2021</t>
+          <t>10/02/2021</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>37–51–54–58–60</t>
+          <t>28–38–42–47–52</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E108" t="n">
         <v>2</v>
       </c>
       <c r="F108" t="n">
-        <v>3479</v>
+        <v>15092</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>$18,474</t>
+          <t>$177,689</t>
         </is>
       </c>
     </row>
@@ -3569,26 +3569,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>09/18/2021</t>
+          <t>09/29/2021</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>5–36–39–45–57</t>
+          <t>2–7–11–17–32</t>
         </is>
       </c>
       <c r="D109" t="n">
         <v>11</v>
       </c>
       <c r="E109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F109" t="n">
-        <v>7699</v>
+        <v>8770</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>$90,232</t>
+          <t>$54,769</t>
         </is>
       </c>
     </row>
@@ -3598,26 +3598,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>09/15/2021</t>
+          <t>09/27/2021</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>1–4–18–46–62</t>
+          <t>21–22–39–44–60</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F110" t="n">
-        <v>5370</v>
+        <v>4965</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>$83,044</t>
+          <t>$26,284</t>
         </is>
       </c>
     </row>
@@ -3627,26 +3627,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>09/13/2021</t>
+          <t>09/25/2021</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>37–40–50–61–63</t>
+          <t>22–23–37–62–63</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E111" t="n">
         <v>3</v>
       </c>
       <c r="F111" t="n">
-        <v>3109</v>
+        <v>9325</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>$19,473</t>
+          <t>$55,118</t>
         </is>
       </c>
     </row>
@@ -3656,26 +3656,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>09/11/2021</t>
+          <t>09/22/2021</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>20–31–38–40–49</t>
+          <t>20–40–47–55–63</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F112" t="n">
-        <v>6641</v>
+        <v>6028</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>$34,612</t>
+          <t>$35,780</t>
         </is>
       </c>
     </row>
@@ -3685,26 +3685,26 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>09/08/2021</t>
+          <t>09/20/2021</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>9–22–41–47–61</t>
+          <t>37–51–54–58–60</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E113" t="n">
         <v>2</v>
       </c>
       <c r="F113" t="n">
-        <v>4510</v>
+        <v>3479</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>$23,724</t>
+          <t>$18,474</t>
         </is>
       </c>
     </row>
@@ -3714,26 +3714,26 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>09/06/2021</t>
+          <t>09/18/2021</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>11–20–22–33–54</t>
+          <t>5–36–39–45–57</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E114" t="n">
         <v>2</v>
       </c>
       <c r="F114" t="n">
-        <v>2437</v>
+        <v>7699</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>$13,828</t>
+          <t>$90,232</t>
         </is>
       </c>
     </row>
@@ -3743,26 +3743,26 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>09/04/2021</t>
+          <t>09/15/2021</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>32–35–40–52–54</t>
+          <t>1–4–18–46–62</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E115" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F115" t="n">
-        <v>5486</v>
+        <v>5370</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>$40,763</t>
+          <t>$83,044</t>
         </is>
       </c>
     </row>
@@ -3772,26 +3772,26 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>09/01/2021</t>
+          <t>09/13/2021</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>10–20–29–48–51</t>
+          <t>37–40–50–61–63</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F116" t="n">
-        <v>4201</v>
+        <v>3109</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>$22,236</t>
+          <t>$19,473</t>
         </is>
       </c>
     </row>
@@ -3801,26 +3801,26 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>08/30/2021</t>
+          <t>09/11/2021</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>3–15–45–51–61</t>
+          <t>20–31–38–40–49</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E117" t="n">
         <v>2</v>
       </c>
       <c r="F117" t="n">
-        <v>2384</v>
+        <v>6641</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>$12,523</t>
+          <t>$34,612</t>
         </is>
       </c>
     </row>
@@ -3830,26 +3830,26 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>08/28/2021</t>
+          <t>09/08/2021</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>12–22–26–46–59</t>
+          <t>9–22–41–47–61</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E118" t="n">
         <v>2</v>
       </c>
       <c r="F118" t="n">
-        <v>5500</v>
+        <v>4510</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>$28,487</t>
+          <t>$23,724</t>
         </is>
       </c>
     </row>
@@ -3859,26 +3859,26 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>08/25/2021</t>
+          <t>09/06/2021</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>27–39–54–56–59</t>
+          <t>11–20–22–33–54</t>
         </is>
       </c>
       <c r="D119" t="n">
         <v>24</v>
       </c>
       <c r="E119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F119" t="n">
-        <v>3782</v>
+        <v>2437</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>$22,540</t>
+          <t>$13,828</t>
         </is>
       </c>
     </row>
@@ -3888,26 +3888,26 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>08/23/2021</t>
+          <t>09/04/2021</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>17–36–47–60–61</t>
+          <t>32–35–40–52–54</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F120" t="n">
-        <v>1802</v>
+        <v>5486</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>$11,540</t>
+          <t>$40,763</t>
         </is>
       </c>
     </row>
@@ -3917,26 +3917,26 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>08/21/2021</t>
+          <t>09/01/2021</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>16–28–36–39–59</t>
+          <t>10–20–29–48–51</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E121" t="n">
         <v>2</v>
       </c>
       <c r="F121" t="n">
-        <v>5049</v>
+        <v>4201</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>$1,026,295</t>
+          <t>$22,236</t>
         </is>
       </c>
     </row>
@@ -3946,26 +3946,26 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>08/18/2021</t>
+          <t>08/30/2021</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>35–36–51–55–61</t>
+          <t>3–15–45–51–61</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E122" t="n">
         <v>2</v>
       </c>
       <c r="F122" t="n">
-        <v>4753</v>
+        <v>2384</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>$1,024,428</t>
+          <t>$12,523</t>
         </is>
       </c>
     </row>
@@ -3975,26 +3975,26 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>08/14/2021</t>
+          <t>08/28/2021</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>6–21–49–65–67</t>
+          <t>12–22–26–46–59</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E123" t="n">
         <v>2</v>
       </c>
       <c r="F123" t="n">
-        <v>4928</v>
+        <v>5500</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>$26,548</t>
+          <t>$28,487</t>
         </is>
       </c>
     </row>
@@ -4004,26 +4004,26 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>08/11/2021</t>
+          <t>08/25/2021</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>12–18–20–29–30</t>
+          <t>27–39–54–56–59</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E124" t="n">
         <v>3</v>
       </c>
       <c r="F124" t="n">
-        <v>4238</v>
+        <v>3782</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>$27,758</t>
+          <t>$22,540</t>
         </is>
       </c>
     </row>
@@ -4033,26 +4033,26 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>08/07/2021</t>
+          <t>08/23/2021</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>7–24–36–54–60</t>
+          <t>17–36–47–60–61</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F125" t="n">
-        <v>4741</v>
+        <v>1802</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>$24,513</t>
+          <t>$11,540</t>
         </is>
       </c>
     </row>
@@ -4062,26 +4062,26 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>08/04/2021</t>
+          <t>08/21/2021</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>5–21–32–36–58</t>
+          <t>16–28–36–39–59</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E126" t="n">
         <v>2</v>
       </c>
       <c r="F126" t="n">
-        <v>3946</v>
+        <v>5049</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>$21,111</t>
+          <t>$1,026,295</t>
         </is>
       </c>
     </row>
@@ -4091,26 +4091,26 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>07/31/2021</t>
+          <t>08/18/2021</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>1–21–22–34–47</t>
+          <t>35–36–51–55–61</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E127" t="n">
         <v>2</v>
       </c>
       <c r="F127" t="n">
-        <v>4505</v>
+        <v>4753</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>$24,120</t>
+          <t>$1,024,428</t>
         </is>
       </c>
     </row>
@@ -4120,26 +4120,26 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>07/28/2021</t>
+          <t>08/14/2021</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>25–30–53–59–60</t>
+          <t>6–21–49–65–67</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F128" t="n">
-        <v>3889</v>
+        <v>4928</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>$73,912</t>
+          <t>$26,548</t>
         </is>
       </c>
     </row>
@@ -4149,26 +4149,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>07/24/2021</t>
+          <t>08/11/2021</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>1–4–11–59–67</t>
+          <t>12–18–20–29–30</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F129" t="n">
-        <v>4261</v>
+        <v>4238</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>$24,125</t>
+          <t>$27,758</t>
         </is>
       </c>
     </row>
@@ -4178,26 +4178,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>07/21/2021</t>
+          <t>08/07/2021</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>27–28–44–67–68</t>
+          <t>7–24–36–54–60</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E130" t="n">
         <v>2</v>
       </c>
       <c r="F130" t="n">
-        <v>3921</v>
+        <v>4741</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>$1,071,075</t>
+          <t>$24,513</t>
         </is>
       </c>
     </row>
@@ -4207,26 +4207,26 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>07/17/2021</t>
+          <t>08/04/2021</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>15–22–38–54–66</t>
+          <t>5–21–32–36–58</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E131" t="n">
         <v>2</v>
       </c>
       <c r="F131" t="n">
-        <v>4139</v>
+        <v>3946</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>$121,736</t>
+          <t>$21,111</t>
         </is>
       </c>
     </row>
@@ -4236,26 +4236,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>07/14/2021</t>
+          <t>07/31/2021</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>33–46–52–59–62</t>
+          <t>1–21–22–34–47</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E132" t="n">
         <v>2</v>
       </c>
       <c r="F132" t="n">
-        <v>3626</v>
+        <v>4505</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>$18,667</t>
+          <t>$24,120</t>
         </is>
       </c>
     </row>
@@ -4265,26 +4265,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>07/10/2021</t>
+          <t>07/28/2021</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>1–5–29–54–62</t>
+          <t>25–30–53–59–60</t>
         </is>
       </c>
       <c r="D133" t="n">
+        <v>5</v>
+      </c>
+      <c r="E133" t="n">
         <v>3</v>
       </c>
-      <c r="E133" t="n">
-        <v>2</v>
-      </c>
       <c r="F133" t="n">
-        <v>3988</v>
+        <v>3889</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>$171,952</t>
+          <t>$73,912</t>
         </is>
       </c>
     </row>
@@ -4294,26 +4294,26 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>07/07/2021</t>
+          <t>07/24/2021</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>8–21–30–49–57</t>
+          <t>1–4–11–59–67</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E134" t="n">
         <v>2</v>
       </c>
       <c r="F134" t="n">
-        <v>3589</v>
+        <v>4261</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>$19,961</t>
+          <t>$24,125</t>
         </is>
       </c>
     </row>
@@ -4323,26 +4323,26 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>07/03/2021</t>
+          <t>07/21/2021</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>26–40–41–55–65</t>
+          <t>27–28–44–67–68</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E135" t="n">
         <v>2</v>
       </c>
       <c r="F135" t="n">
-        <v>4074</v>
+        <v>3921</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>$21,576</t>
+          <t>$1,071,075</t>
         </is>
       </c>
     </row>
@@ -4352,26 +4352,26 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>06/30/2021</t>
+          <t>07/17/2021</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>24–29–50–65–66</t>
+          <t>15–22–38–54–66</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E136" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F136" t="n">
-        <v>3195</v>
+        <v>4139</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>$73,597</t>
+          <t>$121,736</t>
         </is>
       </c>
     </row>
@@ -4381,26 +4381,26 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>06/26/2021</t>
+          <t>07/14/2021</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>8–31–39–43–60</t>
+          <t>33–46–52–59–62</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F137" t="n">
-        <v>3541</v>
+        <v>3626</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>$22,713</t>
+          <t>$18,667</t>
         </is>
       </c>
     </row>
@@ -4410,26 +4410,26 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>06/23/2021</t>
+          <t>07/10/2021</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>13–20–40–51–63</t>
+          <t>1–5–29–54–62</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F138" t="n">
-        <v>2796</v>
+        <v>3988</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>$16,908</t>
+          <t>$171,952</t>
         </is>
       </c>
     </row>
@@ -4439,26 +4439,26 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>06/19/2021</t>
+          <t>07/07/2021</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>4–22–35–38–39</t>
+          <t>8–21–30–49–57</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E139" t="n">
         <v>2</v>
       </c>
       <c r="F139" t="n">
-        <v>3396</v>
+        <v>3589</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>$18,109</t>
+          <t>$19,961</t>
         </is>
       </c>
     </row>
@@ -4468,26 +4468,26 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>06/16/2021</t>
+          <t>07/03/2021</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>19–29–34–44–50</t>
+          <t>26–40–41–55–65</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E140" t="n">
         <v>2</v>
       </c>
       <c r="F140" t="n">
-        <v>3102</v>
+        <v>4074</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>$15,857</t>
+          <t>$21,576</t>
         </is>
       </c>
     </row>
@@ -4497,26 +4497,26 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>06/12/2021</t>
+          <t>06/30/2021</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>8–25–34–38–41</t>
+          <t>24–29–50–65–66</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F141" t="n">
-        <v>3386</v>
+        <v>3195</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>$21,343</t>
+          <t>$73,597</t>
         </is>
       </c>
     </row>
@@ -4526,26 +4526,26 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>06/09/2021</t>
+          <t>06/26/2021</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>19–28–46–50–54</t>
+          <t>8–31–39–43–60</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F142" t="n">
-        <v>3205</v>
+        <v>3541</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>$17,283</t>
+          <t>$22,713</t>
         </is>
       </c>
     </row>
@@ -4555,26 +4555,26 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>06/05/2021</t>
+          <t>06/23/2021</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>44–52–54–64–69</t>
+          <t>13–20–40–51–63</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="E143" t="n">
         <v>3</v>
       </c>
       <c r="F143" t="n">
-        <v>5295</v>
+        <v>2796</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>$32,299</t>
+          <t>$16,908</t>
         </is>
       </c>
     </row>
@@ -4584,26 +4584,26 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>06/02/2021</t>
+          <t>06/19/2021</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>6–7–11–66–67</t>
+          <t>4–22–35–38–39</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F144" t="n">
-        <v>4672</v>
+        <v>3396</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>$30,150</t>
+          <t>$18,109</t>
         </is>
       </c>
     </row>
@@ -4613,26 +4613,84 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>05/29/2021</t>
+          <t>06/16/2021</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>11–13–22–27–46</t>
+          <t>19–29–34–44–50</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E145" t="n">
         <v>2</v>
       </c>
       <c r="F145" t="n">
-        <v>5088</v>
+        <v>3102</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>$27,508</t>
+          <t>$15,857</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>06/12/2021</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>8–25–34–38–41</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10</v>
+      </c>
+      <c r="E146" t="n">
+        <v>3</v>
+      </c>
+      <c r="F146" t="n">
+        <v>3386</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>$21,343</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>06/09/2021</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>19–28–46–50–54</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>9</v>
+      </c>
+      <c r="E147" t="n">
+        <v>2</v>
+      </c>
+      <c r="F147" t="n">
+        <v>3205</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>$17,283</t>
         </is>
       </c>
     </row>

--- a/lottopy_site/lottopy/lottopy_web_edition/lotto.xlsx
+++ b/lottopy_site/lottopy/lottopy_web_edition/lotto.xlsx
@@ -466,26 +466,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>06/06/2022</t>
+          <t>06/08/2022</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2–10–35–44–46</t>
+          <t>22–39–43–62–64</t>
         </is>
       </c>
       <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
       <c r="F2" t="n">
-        <v>1955</v>
+        <v>3215</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>$10,321</t>
+          <t>$23,360</t>
         </is>
       </c>
     </row>
@@ -495,26 +495,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06/04/2022</t>
+          <t>06/06/2022</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14–16–36–52–60</t>
+          <t>2–10–35–44–46</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>3519</v>
+        <v>1955</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>$21,345</t>
+          <t>$10,321</t>
         </is>
       </c>
     </row>
@@ -524,26 +524,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>06/01/2022</t>
+          <t>06/04/2022</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11–41–56–57–63</t>
+          <t>14–16–36–52–60</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>2413</v>
+        <v>3519</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>$63,352</t>
+          <t>$21,345</t>
         </is>
       </c>
     </row>
@@ -553,26 +553,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>05/30/2022</t>
+          <t>06/01/2022</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>27–28–51–68–69</t>
+          <t>11–41–56–57–63</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>1634</v>
+        <v>2413</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>$8,412</t>
+          <t>$63,352</t>
         </is>
       </c>
     </row>
@@ -582,26 +582,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05/28/2022</t>
+          <t>05/30/2022</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2–39–50–61–66</t>
+          <t>27–28–51–68–69</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>3417</v>
+        <v>1634</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>$17,916</t>
+          <t>$8,412</t>
         </is>
       </c>
     </row>
@@ -611,26 +611,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>05/25/2022</t>
+          <t>05/28/2022</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19–28–39–42–57</t>
+          <t>2–39–50–61–66</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>2505</v>
+        <v>3417</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>$16,022</t>
+          <t>$17,916</t>
         </is>
       </c>
     </row>
@@ -640,26 +640,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>05/23/2022</t>
+          <t>05/25/2022</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1–33–37–39–42</t>
+          <t>19–28–39–42–57</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>1861</v>
+        <v>2505</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>$10,215</t>
+          <t>$16,022</t>
         </is>
       </c>
     </row>
@@ -669,26 +669,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>05/21/2022</t>
+          <t>05/23/2022</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14–15–25–52–58</t>
+          <t>1–33–37–39–42</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>3589</v>
+        <v>1861</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>$19,081</t>
+          <t>$10,215</t>
         </is>
       </c>
     </row>
@@ -698,26 +698,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>05/18/2022</t>
+          <t>05/21/2022</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>40–41–58–64–65</t>
+          <t>14–15–25–52–58</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>2497</v>
+        <v>3589</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>$15,527</t>
+          <t>$19,081</t>
         </is>
       </c>
     </row>
@@ -727,26 +727,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>05/16/2022</t>
+          <t>05/18/2022</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7–15–22–36–64</t>
+          <t>40–41–58–64–65</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>2051</v>
+        <v>2497</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>$11,124</t>
+          <t>$15,527</t>
         </is>
       </c>
     </row>
@@ -756,26 +756,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>05/14/2022</t>
+          <t>05/16/2022</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6–40–41–45–52</t>
+          <t>7–15–22–36–64</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>3364</v>
+        <v>2051</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>$21,033</t>
+          <t>$11,124</t>
         </is>
       </c>
     </row>
@@ -785,26 +785,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>05/11/2022</t>
+          <t>05/14/2022</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5–7–61–63–69</t>
+          <t>6–40–41–45–52</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>2266</v>
+        <v>3364</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$12,461</t>
+          <t>$21,033</t>
         </is>
       </c>
     </row>
@@ -814,26 +814,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>05/09/2022</t>
+          <t>05/11/2022</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18–30–35–52–56</t>
+          <t>5–7–61–63–69</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>1660</v>
+        <v>2266</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>$8,855</t>
+          <t>$12,461</t>
         </is>
       </c>
     </row>
@@ -843,26 +843,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>05/07/2022</t>
+          <t>05/09/2022</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4–5–6–28–67</t>
+          <t>18–30–35–52–56</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>3376</v>
+        <v>1660</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>$18,445</t>
+          <t>$8,855</t>
         </is>
       </c>
     </row>
@@ -872,26 +872,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>05/04/2022</t>
+          <t>05/07/2022</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>37–39–55–63–69</t>
+          <t>4–5–6–28–67</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>2278</v>
+        <v>3376</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>$11,925</t>
+          <t>$18,445</t>
         </is>
       </c>
     </row>
@@ -901,26 +901,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>05/02/2022</t>
+          <t>05/04/2022</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18–27–33–39–44</t>
+          <t>37–39–55–63–69</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>1662</v>
+        <v>2278</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>$15,265</t>
+          <t>$11,925</t>
         </is>
       </c>
     </row>
@@ -930,26 +930,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>04/30/2022</t>
+          <t>05/02/2022</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14–21–37–44–63</t>
+          <t>18–27–33–39–44</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>2815</v>
+        <v>1662</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>$17,825</t>
+          <t>$15,265</t>
         </is>
       </c>
     </row>
@@ -959,26 +959,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>04/27/2022</t>
+          <t>04/30/2022</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>11–36–61–62–68</t>
+          <t>14–21–37–44–63</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>6965</v>
+        <v>2815</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>$35,750</t>
+          <t>$17,825</t>
         </is>
       </c>
     </row>
@@ -988,26 +988,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>04/25/2022</t>
+          <t>04/27/2022</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>12–18–20–39–61</t>
+          <t>11–36–61–62–68</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>4259</v>
+        <v>6965</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>$22,856</t>
+          <t>$35,750</t>
         </is>
       </c>
     </row>
@@ -1017,26 +1017,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>04/23/2022</t>
+          <t>04/25/2022</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10–39–47–49–56</t>
+          <t>12–18–20–39–61</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>6457</v>
+        <v>4259</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>$38,869</t>
+          <t>$22,856</t>
         </is>
       </c>
     </row>
@@ -1046,26 +1046,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>04/20/2022</t>
+          <t>04/23/2022</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20–30–45–55–56</t>
+          <t>10–39–47–49–56</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>3844</v>
+        <v>6457</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>$20,255</t>
+          <t>$38,869</t>
         </is>
       </c>
     </row>
@@ -1075,26 +1075,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>04/18/2022</t>
+          <t>04/20/2022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>8–33–55–59–62</t>
+          <t>20–30–45–55–56</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>2688</v>
+        <v>3844</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>$14,224</t>
+          <t>$20,255</t>
         </is>
       </c>
     </row>
@@ -1104,26 +1104,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>04/16/2022</t>
+          <t>04/18/2022</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15–21–32–62–65</t>
+          <t>8–33–55–59–62</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>5160</v>
+        <v>2688</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>$39,825</t>
+          <t>$14,224</t>
         </is>
       </c>
     </row>
@@ -1133,26 +1133,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>04/13/2022</t>
+          <t>04/16/2022</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>14–16–41–63–68</t>
+          <t>15–21–32–62–65</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>3741</v>
+        <v>5160</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>$19,516</t>
+          <t>$39,825</t>
         </is>
       </c>
     </row>
@@ -1162,26 +1162,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>04/11/2022</t>
+          <t>04/13/2022</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5–7–24–31–34</t>
+          <t>14–16–41–63–68</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>2417</v>
+        <v>3741</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>$14,052</t>
+          <t>$19,516</t>
         </is>
       </c>
     </row>
@@ -1191,26 +1191,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>04/09/2022</t>
+          <t>04/11/2022</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>6–16–31–62–66</t>
+          <t>5–7–24–31–34</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>4503</v>
+        <v>2417</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>$23,731</t>
+          <t>$14,052</t>
         </is>
       </c>
     </row>
@@ -1220,26 +1220,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>04/06/2022</t>
+          <t>04/09/2022</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>6–42–45–47–64</t>
+          <t>6–16–31–62–66</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>18</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>3310</v>
+        <v>4503</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>$20,766</t>
+          <t>$23,731</t>
         </is>
       </c>
     </row>
@@ -1249,26 +1249,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>04/04/2022</t>
+          <t>04/06/2022</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2–32–39–46–69</t>
+          <t>6–42–45–47–64</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>2330</v>
+        <v>3310</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>$62,603</t>
+          <t>$20,766</t>
         </is>
       </c>
     </row>
@@ -1278,26 +1278,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>04/02/2022</t>
+          <t>04/04/2022</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6–28–47–58–59</t>
+          <t>2–32–39–46–69</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>4468</v>
+        <v>2330</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>$23,828</t>
+          <t>$62,603</t>
         </is>
       </c>
     </row>
@@ -1307,26 +1307,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>03/30/2022</t>
+          <t>04/02/2022</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3–7–21–31–37</t>
+          <t>6–28–47–58–59</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>3227</v>
+        <v>4468</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>$21,396</t>
+          <t>$23,828</t>
         </is>
       </c>
     </row>
@@ -1336,26 +1336,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>03/28/2022</t>
+          <t>03/30/2022</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>11–18–39–58–62</t>
+          <t>3–7–21–31–37</t>
         </is>
       </c>
       <c r="D32" t="n">
+        <v>11</v>
+      </c>
+      <c r="E32" t="n">
         <v>3</v>
       </c>
-      <c r="E32" t="n">
-        <v>2</v>
-      </c>
       <c r="F32" t="n">
-        <v>2106</v>
+        <v>3227</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>$11,495</t>
+          <t>$21,396</t>
         </is>
       </c>
     </row>
@@ -1365,26 +1365,26 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>03/26/2022</t>
+          <t>03/28/2022</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2–10–50–59–61</t>
+          <t>11–18–39–58–62</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>3931</v>
+        <v>2106</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>$24,782</t>
+          <t>$11,495</t>
         </is>
       </c>
     </row>
@@ -1394,26 +1394,26 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>03/23/2022</t>
+          <t>03/26/2022</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>31–32–37–38–48</t>
+          <t>2–10–50–59–61</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" t="n">
-        <v>2814</v>
+        <v>3931</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>$65,889</t>
+          <t>$24,782</t>
         </is>
       </c>
     </row>
@@ -1423,26 +1423,26 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>03/21/2022</t>
+          <t>03/23/2022</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1–15–26–63–65</t>
+          <t>31–32–37–38–48</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>1797</v>
+        <v>2814</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>$9,529</t>
+          <t>$65,889</t>
         </is>
       </c>
     </row>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>03/19/2022</t>
+          <t>03/21/2022</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>8–9–18–48–52</t>
+          <t>1–15–26–63–65</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E36" t="n">
         <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>3802</v>
+        <v>1797</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>$70,218</t>
+          <t>$9,529</t>
         </is>
       </c>
     </row>
@@ -1481,26 +1481,26 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>03/16/2022</t>
+          <t>03/19/2022</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3–28–34–35–58</t>
+          <t>8–9–18–48–52</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
         <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>2724</v>
+        <v>3802</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>$14,515</t>
+          <t>$70,218</t>
         </is>
       </c>
     </row>
@@ -1510,26 +1510,26 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>03/14/2022</t>
+          <t>03/16/2022</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>21–28–32–44–49</t>
+          <t>3–28–34–35–58</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>1860</v>
+        <v>2724</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>$11,769</t>
+          <t>$14,515</t>
         </is>
       </c>
     </row>
@@ -1539,26 +1539,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>03/12/2022</t>
+          <t>03/14/2022</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>19–20–37–39–61</t>
+          <t>21–28–32–44–49</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" t="n">
-        <v>3361</v>
+        <v>1860</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>$17,986</t>
+          <t>$11,769</t>
         </is>
       </c>
     </row>
@@ -1568,26 +1568,26 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>03/09/2022</t>
+          <t>03/12/2022</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>13–22–34–51–67</t>
+          <t>19–20–37–39–61</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E40" t="n">
         <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>2618</v>
+        <v>3361</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>$14,396</t>
+          <t>$17,986</t>
         </is>
       </c>
     </row>
@@ -1597,26 +1597,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>03/07/2022</t>
+          <t>03/09/2022</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>10–43–55–59–67</t>
+          <t>13–22–34–51–67</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>1619</v>
+        <v>2618</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>$160,016</t>
+          <t>$14,396</t>
         </is>
       </c>
     </row>
@@ -1626,26 +1626,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>03/05/2022</t>
+          <t>03/07/2022</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>8–23–37–52–63</t>
+          <t>10–43–55–59–67</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>3927</v>
+        <v>1619</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>$20,702</t>
+          <t>$160,016</t>
         </is>
       </c>
     </row>
@@ -1655,26 +1655,26 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>03/02/2022</t>
+          <t>03/05/2022</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>19–37–48–61–63</t>
+          <t>8–23–37–52–63</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E43" t="n">
         <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>2488</v>
+        <v>3927</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>$13,667</t>
+          <t>$20,702</t>
         </is>
       </c>
     </row>
@@ -1684,26 +1684,26 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>02/28/2022</t>
+          <t>03/02/2022</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>7–21–39–47–55</t>
+          <t>19–37–48–61–63</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E44" t="n">
         <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>1715</v>
+        <v>2488</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>$9,855</t>
+          <t>$13,667</t>
         </is>
       </c>
     </row>
@@ -1713,26 +1713,26 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>02/26/2022</t>
+          <t>02/28/2022</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>15–32–36–48–64</t>
+          <t>7–21–39–47–55</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>19</v>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>3228</v>
+        <v>1715</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>$20,406</t>
+          <t>$9,855</t>
         </is>
       </c>
     </row>
@@ -1742,26 +1742,26 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>02/23/2022</t>
+          <t>02/26/2022</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>6–17–21–35–64</t>
+          <t>15–32–36–48–64</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>2402</v>
+        <v>3228</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>$12,893</t>
+          <t>$20,406</t>
         </is>
       </c>
     </row>
@@ -1771,26 +1771,26 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>02/21/2022</t>
+          <t>02/23/2022</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2–36–37–45–69</t>
+          <t>6–17–21–35–64</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E47" t="n">
         <v>2</v>
       </c>
       <c r="F47" t="n">
-        <v>1699</v>
+        <v>2402</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>$9,608</t>
+          <t>$12,893</t>
         </is>
       </c>
     </row>
@@ -1800,26 +1800,26 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>02/19/2022</t>
+          <t>02/21/2022</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3–10–15–33–42</t>
+          <t>2–36–37–45–69</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
         <v>2</v>
       </c>
       <c r="F48" t="n">
-        <v>3430</v>
+        <v>1699</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>$18,437</t>
+          <t>$9,608</t>
         </is>
       </c>
     </row>
@@ -1829,26 +1829,26 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>02/16/2022</t>
+          <t>02/19/2022</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>22–30–40–42–48</t>
+          <t>3–10–15–33–42</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E49" t="n">
         <v>2</v>
       </c>
       <c r="F49" t="n">
-        <v>2213</v>
+        <v>3430</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>$11,803</t>
+          <t>$18,437</t>
         </is>
       </c>
     </row>
@@ -1858,26 +1858,26 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>02/14/2022</t>
+          <t>02/16/2022</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>16–25–27–49–55</t>
+          <t>22–30–40–42–48</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F50" t="n">
-        <v>2080</v>
+        <v>2213</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>$63,441</t>
+          <t>$11,803</t>
         </is>
       </c>
     </row>
@@ -1887,26 +1887,26 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>02/12/2022</t>
+          <t>02/14/2022</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>8–10–21–41–62</t>
+          <t>16–25–27–49–55</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E51" t="n">
         <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>4805</v>
+        <v>2080</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>$30,505</t>
+          <t>$63,441</t>
         </is>
       </c>
     </row>
@@ -1916,26 +1916,26 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>02/09/2022</t>
+          <t>02/12/2022</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2–17–33–51–63</t>
+          <t>8–10–21–41–62</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F52" t="n">
-        <v>3170</v>
+        <v>4805</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>$17,047</t>
+          <t>$30,505</t>
         </is>
       </c>
     </row>
@@ -1945,26 +1945,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>02/07/2022</t>
+          <t>02/09/2022</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>5–15–38–47–65</t>
+          <t>2–17–33–51–63</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>2219</v>
+        <v>3170</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>$14,620</t>
+          <t>$17,047</t>
         </is>
       </c>
     </row>
@@ -1974,26 +1974,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>02/05/2022</t>
+          <t>02/07/2022</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>5–16–27–39–61</t>
+          <t>5–15–38–47–65</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54" t="n">
-        <v>3910</v>
+        <v>2219</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>$70,790</t>
+          <t>$14,620</t>
         </is>
       </c>
     </row>
@@ -2003,26 +2003,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>02/02/2022</t>
+          <t>02/05/2022</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>18–29–33–62–63</t>
+          <t>5–16–27–39–61</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>2852</v>
+        <v>3910</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>$17,682</t>
+          <t>$70,790</t>
         </is>
       </c>
     </row>
@@ -2032,26 +2032,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01/31/2022</t>
+          <t>02/02/2022</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10–15–51–61–69</t>
+          <t>18–29–33–62–63</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E56" t="n">
         <v>3</v>
       </c>
       <c r="F56" t="n">
-        <v>1877</v>
+        <v>2852</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>$12,115</t>
+          <t>$17,682</t>
         </is>
       </c>
     </row>
@@ -2061,26 +2061,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01/29/2022</t>
+          <t>01/31/2022</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2–15–38–54–65</t>
+          <t>10–15–51–61–69</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
-        <v>3836</v>
+        <v>1877</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>$27,233</t>
+          <t>$12,115</t>
         </is>
       </c>
     </row>
@@ -2090,26 +2090,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01/26/2022</t>
+          <t>01/29/2022</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>4–11–38–49–69</t>
+          <t>2–15–38–54–65</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F58" t="n">
-        <v>2390</v>
+        <v>3836</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>$15,230</t>
+          <t>$27,233</t>
         </is>
       </c>
     </row>
@@ -2119,12 +2119,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01/24/2022</t>
+          <t>01/26/2022</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>11–29–30–47–53</t>
+          <t>4–11–38–49–69</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2134,11 +2134,11 @@
         <v>3</v>
       </c>
       <c r="F59" t="n">
-        <v>1657</v>
+        <v>2390</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>$10,526</t>
+          <t>$15,230</t>
         </is>
       </c>
     </row>
@@ -2148,26 +2148,26 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01/22/2022</t>
+          <t>01/24/2022</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>8–14–33–36–67</t>
+          <t>11–29–30–47–53</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F60" t="n">
-        <v>3412</v>
+        <v>1657</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>$17,955</t>
+          <t>$10,526</t>
         </is>
       </c>
     </row>
@@ -2177,26 +2177,26 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01/19/2022</t>
+          <t>01/22/2022</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>11–15–43–55–61</t>
+          <t>8–14–33–36–67</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
-        <v>2614</v>
+        <v>3412</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>$16,581</t>
+          <t>$17,955</t>
         </is>
       </c>
     </row>
@@ -2206,26 +2206,26 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01/17/2022</t>
+          <t>01/19/2022</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9–24–35–46–65</t>
+          <t>11–15–43–55–61</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F62" t="n">
-        <v>1152</v>
+        <v>2614</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>$6,245</t>
+          <t>$16,581</t>
         </is>
       </c>
     </row>
@@ -2235,26 +2235,26 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01/15/2022</t>
+          <t>01/17/2022</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>3–18–37–51–59</t>
+          <t>9–24–35–46–65</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E63" t="n">
         <v>2</v>
       </c>
       <c r="F63" t="n">
-        <v>4389</v>
+        <v>1152</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>$23,619</t>
+          <t>$6,245</t>
         </is>
       </c>
     </row>
@@ -2264,26 +2264,26 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01/12/2022</t>
+          <t>01/15/2022</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>12–21–22–30–33</t>
+          <t>3–18–37–51–59</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
-        <v>2782</v>
+        <v>4389</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>$21,778</t>
+          <t>$23,619</t>
         </is>
       </c>
     </row>
@@ -2293,26 +2293,26 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/12/2022</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>14–17–18–21–27</t>
+          <t>12–21–22–30–33</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F65" t="n">
-        <v>1968</v>
+        <v>2782</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>$10,941</t>
+          <t>$21,778</t>
         </is>
       </c>
     </row>
@@ -2322,26 +2322,26 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01/08/2022</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>20–21–36–60–65</t>
+          <t>14–17–18–21–27</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E66" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F66" t="n">
-        <v>4143</v>
+        <v>1968</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>$49,179</t>
+          <t>$10,941</t>
         </is>
       </c>
     </row>
@@ -2351,26 +2351,26 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01/05/2022</t>
+          <t>01/08/2022</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>6–14–25–33–46</t>
+          <t>20–21–36–60–65</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F67" t="n">
-        <v>17059</v>
+        <v>4143</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>$136,964</t>
+          <t>$49,179</t>
         </is>
       </c>
     </row>
@@ -2380,26 +2380,26 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01/03/2022</t>
+          <t>01/05/2022</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2–13–32–33–48</t>
+          <t>6–14–25–33–46</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E68" t="n">
         <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>9057</v>
+        <v>17059</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>$47,939</t>
+          <t>$136,964</t>
         </is>
       </c>
     </row>
@@ -2409,26 +2409,26 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/03/2022</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>6–12–39–48–50</t>
+          <t>2–13–32–33–48</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E69" t="n">
         <v>2</v>
       </c>
       <c r="F69" t="n">
-        <v>15004</v>
+        <v>9057</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>$78,416</t>
+          <t>$47,939</t>
         </is>
       </c>
     </row>
@@ -2438,26 +2438,26 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>12/29/2021</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2–6–9–33–39</t>
+          <t>6–12–39–48–50</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E70" t="n">
         <v>2</v>
       </c>
       <c r="F70" t="n">
-        <v>8073</v>
+        <v>15004</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>$192,549</t>
+          <t>$78,416</t>
         </is>
       </c>
     </row>
@@ -2467,26 +2467,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>12/27/2021</t>
+          <t>12/29/2021</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>36–38–45–62–64</t>
+          <t>2–6–9–33–39</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E71" t="n">
         <v>2</v>
       </c>
       <c r="F71" t="n">
-        <v>4851</v>
+        <v>8073</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>$25,733</t>
+          <t>$192,549</t>
         </is>
       </c>
     </row>
@@ -2496,26 +2496,26 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12/25/2021</t>
+          <t>12/27/2021</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>27–29–45–55–58</t>
+          <t>36–38–45–62–64</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F72" t="n">
-        <v>7884</v>
+        <v>4851</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>$46,299</t>
+          <t>$25,733</t>
         </is>
       </c>
     </row>
@@ -2525,26 +2525,26 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12/22/2021</t>
+          <t>12/25/2021</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>7–16–19–48–68</t>
+          <t>27–29–45–55–58</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
-        <v>4413</v>
+        <v>7884</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>$123,861</t>
+          <t>$46,299</t>
         </is>
       </c>
     </row>
@@ -2554,26 +2554,26 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12/20/2021</t>
+          <t>12/22/2021</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2–13–23–34–66</t>
+          <t>7–16–19–48–68</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F74" t="n">
-        <v>2901</v>
+        <v>4413</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>$20,406</t>
+          <t>$123,861</t>
         </is>
       </c>
     </row>
@@ -2583,26 +2583,26 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>12/18/2021</t>
+          <t>12/20/2021</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2–6–24–51–61</t>
+          <t>2–13–23–34–66</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
-        <v>5456</v>
+        <v>2901</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>$29,465</t>
+          <t>$20,406</t>
         </is>
       </c>
     </row>
@@ -2612,26 +2612,26 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>12/15/2021</t>
+          <t>12/18/2021</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>19–20–40–42–59</t>
+          <t>2–6–24–51–61</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F76" t="n">
-        <v>4068</v>
+        <v>5456</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>$25,115</t>
+          <t>$29,465</t>
         </is>
       </c>
     </row>
@@ -2641,26 +2641,26 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>12/13/2021</t>
+          <t>12/15/2021</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>10–30–37–53–59</t>
+          <t>19–20–40–42–59</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" t="n">
-        <v>2651</v>
+        <v>4068</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>$13,704</t>
+          <t>$25,115</t>
         </is>
       </c>
     </row>
@@ -2670,26 +2670,26 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>12/11/2021</t>
+          <t>12/13/2021</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>3–25–44–53–64</t>
+          <t>10–30–37–53–59</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E78" t="n">
         <v>2</v>
       </c>
       <c r="F78" t="n">
-        <v>5553</v>
+        <v>2651</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>$79,318</t>
+          <t>$13,704</t>
         </is>
       </c>
     </row>
@@ -2699,26 +2699,26 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>12/08/2021</t>
+          <t>12/11/2021</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>3–7–33–50–69</t>
+          <t>3–25–44–53–64</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E79" t="n">
         <v>2</v>
       </c>
       <c r="F79" t="n">
-        <v>3721</v>
+        <v>5553</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>$19,905</t>
+          <t>$79,318</t>
         </is>
       </c>
     </row>
@@ -2728,26 +2728,26 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>12/06/2021</t>
+          <t>12/08/2021</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>3–21–38–50–59</t>
+          <t>3–7–33–50–69</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="E80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F80" t="n">
-        <v>2438</v>
+        <v>3721</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>$16,101</t>
+          <t>$19,905</t>
         </is>
       </c>
     </row>
@@ -2757,26 +2757,26 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>12/04/2021</t>
+          <t>12/06/2021</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>10–40–45–56–67</t>
+          <t>3–21–38–50–59</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F81" t="n">
-        <v>4459</v>
+        <v>2438</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>$23,515</t>
+          <t>$16,101</t>
         </is>
       </c>
     </row>
@@ -2786,26 +2786,26 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>12/01/2021</t>
+          <t>12/04/2021</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>12–15–38–57–63</t>
+          <t>10–40–45–56–67</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
         <v>2</v>
       </c>
       <c r="F82" t="n">
-        <v>3559</v>
+        <v>4459</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>$19,369</t>
+          <t>$23,515</t>
         </is>
       </c>
     </row>
@@ -2815,26 +2815,26 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>11/29/2021</t>
+          <t>12/01/2021</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>18–26–28–38–47</t>
+          <t>12–15–38–57–63</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E83" t="n">
         <v>2</v>
       </c>
       <c r="F83" t="n">
-        <v>2308</v>
+        <v>3559</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>$12,206</t>
+          <t>$19,369</t>
         </is>
       </c>
     </row>
@@ -2844,26 +2844,26 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>11/27/2021</t>
+          <t>11/29/2021</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>8–32–55–64–66</t>
+          <t>18–26–28–38–47</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E84" t="n">
         <v>2</v>
       </c>
       <c r="F84" t="n">
-        <v>4202</v>
+        <v>2308</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>$22,061</t>
+          <t>$12,206</t>
         </is>
       </c>
     </row>
@@ -2873,26 +2873,26 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>11/24/2021</t>
+          <t>11/27/2021</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>10–16–32–63–65</t>
+          <t>8–32–55–64–66</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E85" t="n">
         <v>2</v>
       </c>
       <c r="F85" t="n">
-        <v>3443</v>
+        <v>4202</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>$18,692</t>
+          <t>$22,061</t>
         </is>
       </c>
     </row>
@@ -2902,26 +2902,26 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>11/22/2021</t>
+          <t>11/24/2021</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>7–20–29–38–67</t>
+          <t>10–16–32–63–65</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E86" t="n">
         <v>2</v>
       </c>
       <c r="F86" t="n">
-        <v>2145</v>
+        <v>3443</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>$11,570</t>
+          <t>$18,692</t>
         </is>
       </c>
     </row>
@@ -2931,26 +2931,26 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>11/20/2021</t>
+          <t>11/22/2021</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>40–43–48–59–69</t>
+          <t>7–20–29–38–67</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F87" t="n">
-        <v>4327</v>
+        <v>2145</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>$27,213</t>
+          <t>$11,570</t>
         </is>
       </c>
     </row>
@@ -2960,26 +2960,26 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>11/17/2021</t>
+          <t>11/20/2021</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>3–16–48–52–60</t>
+          <t>40–43–48–59–69</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E88" t="n">
         <v>3</v>
       </c>
       <c r="F88" t="n">
-        <v>2671</v>
+        <v>4327</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>$16,328</t>
+          <t>$27,213</t>
         </is>
       </c>
     </row>
@@ -2989,26 +2989,26 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>11/15/2021</t>
+          <t>11/17/2021</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>5–31–34–51–53</t>
+          <t>3–16–48–52–60</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F89" t="n">
-        <v>1980</v>
+        <v>2671</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>$10,688</t>
+          <t>$16,328</t>
         </is>
       </c>
     </row>
@@ -3018,26 +3018,26 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>11/13/2021</t>
+          <t>11/15/2021</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>8–15–26–35–45</t>
+          <t>5–31–34–51–53</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F90" t="n">
-        <v>4269</v>
+        <v>1980</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>$28,180</t>
+          <t>$10,688</t>
         </is>
       </c>
     </row>
@@ -3047,26 +3047,26 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>11/10/2021</t>
+          <t>11/13/2021</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>19–25–43–46–48</t>
+          <t>8–15–26–35–45</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>2906</v>
+        <v>4269</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>$15,508</t>
+          <t>$28,180</t>
         </is>
       </c>
     </row>
@@ -3076,26 +3076,26 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>11/08/2021</t>
+          <t>11/10/2021</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>21–46–47–57–62</t>
+          <t>19–25–43–46–48</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
-        <v>2026</v>
+        <v>2906</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>$12,653</t>
+          <t>$15,508</t>
         </is>
       </c>
     </row>
@@ -3105,26 +3105,26 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>11/06/2021</t>
+          <t>11/08/2021</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>8–30–48–57–64</t>
+          <t>21–46–47–57–62</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
-        <v>4093</v>
+        <v>2026</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>$21,522</t>
+          <t>$12,653</t>
         </is>
       </c>
     </row>
@@ -3134,26 +3134,26 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>11/03/2021</t>
+          <t>11/06/2021</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1–2–24–50–57</t>
+          <t>8–30–48–57–64</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E94" t="n">
         <v>2</v>
       </c>
       <c r="F94" t="n">
-        <v>3074</v>
+        <v>4093</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>$16,272</t>
+          <t>$21,522</t>
         </is>
       </c>
     </row>
@@ -3163,26 +3163,26 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>11/01/2021</t>
+          <t>11/03/2021</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>9–25–34–44–45</t>
+          <t>1–2–24–50–57</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>2018</v>
+        <v>3074</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>$13,357</t>
+          <t>$16,272</t>
         </is>
       </c>
     </row>
@@ -3192,26 +3192,26 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>10/30/2021</t>
+          <t>11/01/2021</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>5–23–28–43–56</t>
+          <t>9–25–34–44–45</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96" t="n">
-        <v>4041</v>
+        <v>2018</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>$21,171</t>
+          <t>$13,357</t>
         </is>
       </c>
     </row>
@@ -3221,26 +3221,26 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>10/27/2021</t>
+          <t>10/30/2021</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>3–6–26–35–51</t>
+          <t>5–23–28–43–56</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E97" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F97" t="n">
-        <v>2840</v>
+        <v>4041</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>$220,953</t>
+          <t>$21,171</t>
         </is>
       </c>
     </row>
@@ -3250,26 +3250,26 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>10/25/2021</t>
+          <t>10/27/2021</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>10–27–29–44–58</t>
+          <t>3–6–26–35–51</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F98" t="n">
-        <v>1976</v>
+        <v>2840</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>$10,611</t>
+          <t>$220,953</t>
         </is>
       </c>
     </row>
@@ -3279,26 +3279,26 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>10/23/2021</t>
+          <t>10/25/2021</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>10–30–51–57–63</t>
+          <t>10–27–29–44–58</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E99" t="n">
         <v>2</v>
       </c>
       <c r="F99" t="n">
-        <v>3513</v>
+        <v>1976</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>$19,214</t>
+          <t>$10,611</t>
         </is>
       </c>
     </row>
@@ -3308,26 +3308,26 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>10/20/2021</t>
+          <t>10/23/2021</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>7–29–36–41–43</t>
+          <t>10–30–51–57–63</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E100" t="n">
         <v>2</v>
       </c>
       <c r="F100" t="n">
-        <v>2859</v>
+        <v>3513</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>$15,376</t>
+          <t>$19,214</t>
         </is>
       </c>
     </row>
@@ -3337,26 +3337,26 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>10/18/2021</t>
+          <t>10/20/2021</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>30–32–48–53–63</t>
+          <t>7–29–36–41–43</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E101" t="n">
         <v>2</v>
       </c>
       <c r="F101" t="n">
-        <v>1820</v>
+        <v>2859</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>$9,952</t>
+          <t>$15,376</t>
         </is>
       </c>
     </row>
@@ -3366,26 +3366,26 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>10/16/2021</t>
+          <t>10/18/2021</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>30–31–41–42–48</t>
+          <t>30–32–48–53–63</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F102" t="n">
-        <v>3640</v>
+        <v>1820</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>$22,644</t>
+          <t>$9,952</t>
         </is>
       </c>
     </row>
@@ -3395,26 +3395,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>10/13/2021</t>
+          <t>10/16/2021</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>23–29–47–59–60</t>
+          <t>30–31–41–42–48</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F103" t="n">
-        <v>2516</v>
+        <v>3640</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>$13,378</t>
+          <t>$22,644</t>
         </is>
       </c>
     </row>
@@ -3424,26 +3424,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>10/11/2021</t>
+          <t>10/13/2021</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>11–20–33–39–65</t>
+          <t>23–29–47–59–60</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F104" t="n">
-        <v>1868</v>
+        <v>2516</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>$11,712</t>
+          <t>$13,378</t>
         </is>
       </c>
     </row>
@@ -3453,26 +3453,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>10/09/2021</t>
+          <t>10/11/2021</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>12–17–30–45–62</t>
+          <t>11–20–33–39–65</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F105" t="n">
-        <v>3781</v>
+        <v>1868</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>$70,136</t>
+          <t>$11,712</t>
         </is>
       </c>
     </row>
@@ -3482,26 +3482,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>10/06/2021</t>
+          <t>10/09/2021</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>1–17–52–58–64</t>
+          <t>12–17–30–45–62</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E106" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F106" t="n">
-        <v>2884</v>
+        <v>3781</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>$32,671</t>
+          <t>$70,136</t>
         </is>
       </c>
     </row>
@@ -3511,26 +3511,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>10/04/2021</t>
+          <t>10/06/2021</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>12–22–54–66–69</t>
+          <t>1–17–52–58–64</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>10668</v>
+        <v>2884</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>$54,601</t>
+          <t>$32,671</t>
         </is>
       </c>
     </row>
@@ -3540,26 +3540,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>10/02/2021</t>
+          <t>10/04/2021</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>28–38–42–47–52</t>
+          <t>12–22–54–66–69</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E108" t="n">
         <v>2</v>
       </c>
       <c r="F108" t="n">
-        <v>15092</v>
+        <v>10668</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>$177,689</t>
+          <t>$54,601</t>
         </is>
       </c>
     </row>
@@ -3569,26 +3569,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>09/29/2021</t>
+          <t>10/02/2021</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2–7–11–17–32</t>
+          <t>28–38–42–47–52</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F109" t="n">
-        <v>8770</v>
+        <v>15092</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>$54,769</t>
+          <t>$177,689</t>
         </is>
       </c>
     </row>
@@ -3598,26 +3598,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>09/27/2021</t>
+          <t>09/29/2021</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>21–22–39–44–60</t>
+          <t>2–7–11–17–32</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F110" t="n">
-        <v>4965</v>
+        <v>8770</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>$26,284</t>
+          <t>$54,769</t>
         </is>
       </c>
     </row>
@@ -3627,26 +3627,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>09/25/2021</t>
+          <t>09/27/2021</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>22–23–37–62–63</t>
+          <t>21–22–39–44–60</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F111" t="n">
-        <v>9325</v>
+        <v>4965</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>$55,118</t>
+          <t>$26,284</t>
         </is>
       </c>
     </row>
@@ -3656,26 +3656,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>09/22/2021</t>
+          <t>09/25/2021</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>20–40–47–55–63</t>
+          <t>22–23–37–62–63</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E112" t="n">
         <v>3</v>
       </c>
       <c r="F112" t="n">
-        <v>6028</v>
+        <v>9325</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>$35,780</t>
+          <t>$55,118</t>
         </is>
       </c>
     </row>
@@ -3685,26 +3685,26 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>09/20/2021</t>
+          <t>09/22/2021</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>37–51–54–58–60</t>
+          <t>20–40–47–55–63</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F113" t="n">
-        <v>3479</v>
+        <v>6028</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>$18,474</t>
+          <t>$35,780</t>
         </is>
       </c>
     </row>
@@ -3714,26 +3714,26 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>09/18/2021</t>
+          <t>09/20/2021</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>5–36–39–45–57</t>
+          <t>37–51–54–58–60</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E114" t="n">
         <v>2</v>
       </c>
       <c r="F114" t="n">
-        <v>7699</v>
+        <v>3479</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>$90,232</t>
+          <t>$18,474</t>
         </is>
       </c>
     </row>
@@ -3743,26 +3743,26 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>09/15/2021</t>
+          <t>09/18/2021</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>1–4–18–46–62</t>
+          <t>5–36–39–45–57</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F115" t="n">
-        <v>5370</v>
+        <v>7699</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>$83,044</t>
+          <t>$90,232</t>
         </is>
       </c>
     </row>
@@ -3772,26 +3772,26 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>09/13/2021</t>
+          <t>09/15/2021</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>37–40–50–61–63</t>
+          <t>1–4–18–46–62</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E116" t="n">
         <v>3</v>
       </c>
       <c r="F116" t="n">
-        <v>3109</v>
+        <v>5370</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>$19,473</t>
+          <t>$83,044</t>
         </is>
       </c>
     </row>
@@ -3801,26 +3801,26 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>09/11/2021</t>
+          <t>09/13/2021</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>20–31–38–40–49</t>
+          <t>37–40–50–61–63</t>
         </is>
       </c>
       <c r="D117" t="n">
         <v>21</v>
       </c>
       <c r="E117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F117" t="n">
-        <v>6641</v>
+        <v>3109</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>$34,612</t>
+          <t>$19,473</t>
         </is>
       </c>
     </row>
@@ -3830,12 +3830,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>09/08/2021</t>
+          <t>09/11/2021</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>9–22–41–47–61</t>
+          <t>20–31–38–40–49</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -3845,11 +3845,11 @@
         <v>2</v>
       </c>
       <c r="F118" t="n">
-        <v>4510</v>
+        <v>6641</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>$23,724</t>
+          <t>$34,612</t>
         </is>
       </c>
     </row>
@@ -3859,26 +3859,26 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>09/06/2021</t>
+          <t>09/08/2021</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>11–20–22–33–54</t>
+          <t>9–22–41–47–61</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E119" t="n">
         <v>2</v>
       </c>
       <c r="F119" t="n">
-        <v>2437</v>
+        <v>4510</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>$13,828</t>
+          <t>$23,724</t>
         </is>
       </c>
     </row>
@@ -3888,26 +3888,26 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>09/04/2021</t>
+          <t>09/06/2021</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>32–35–40–52–54</t>
+          <t>11–20–22–33–54</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E120" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F120" t="n">
-        <v>5486</v>
+        <v>2437</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>$40,763</t>
+          <t>$13,828</t>
         </is>
       </c>
     </row>
@@ -3917,26 +3917,26 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>09/01/2021</t>
+          <t>09/04/2021</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>10–20–29–48–51</t>
+          <t>32–35–40–52–54</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E121" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F121" t="n">
-        <v>4201</v>
+        <v>5486</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>$22,236</t>
+          <t>$40,763</t>
         </is>
       </c>
     </row>
@@ -3946,26 +3946,26 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>08/30/2021</t>
+          <t>09/01/2021</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>3–15–45–51–61</t>
+          <t>10–20–29–48–51</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E122" t="n">
         <v>2</v>
       </c>
       <c r="F122" t="n">
-        <v>2384</v>
+        <v>4201</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>$12,523</t>
+          <t>$22,236</t>
         </is>
       </c>
     </row>
@@ -3975,26 +3975,26 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>08/28/2021</t>
+          <t>08/30/2021</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>12–22–26–46–59</t>
+          <t>3–15–45–51–61</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E123" t="n">
         <v>2</v>
       </c>
       <c r="F123" t="n">
-        <v>5500</v>
+        <v>2384</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>$28,487</t>
+          <t>$12,523</t>
         </is>
       </c>
     </row>
@@ -4004,26 +4004,26 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>08/25/2021</t>
+          <t>08/28/2021</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>27–39–54–56–59</t>
+          <t>12–22–26–46–59</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F124" t="n">
-        <v>3782</v>
+        <v>5500</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>$22,540</t>
+          <t>$28,487</t>
         </is>
       </c>
     </row>
@@ -4033,26 +4033,26 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>08/23/2021</t>
+          <t>08/25/2021</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>17–36–47–60–61</t>
+          <t>27–39–54–56–59</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E125" t="n">
         <v>3</v>
       </c>
       <c r="F125" t="n">
-        <v>1802</v>
+        <v>3782</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>$11,540</t>
+          <t>$22,540</t>
         </is>
       </c>
     </row>
@@ -4062,26 +4062,26 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>08/21/2021</t>
+          <t>08/23/2021</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>16–28–36–39–59</t>
+          <t>17–36–47–60–61</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F126" t="n">
-        <v>5049</v>
+        <v>1802</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>$1,026,295</t>
+          <t>$11,540</t>
         </is>
       </c>
     </row>
@@ -4091,26 +4091,26 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>08/18/2021</t>
+          <t>08/21/2021</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>35–36–51–55–61</t>
+          <t>16–28–36–39–59</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="E127" t="n">
         <v>2</v>
       </c>
       <c r="F127" t="n">
-        <v>4753</v>
+        <v>5049</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>$1,024,428</t>
+          <t>$1,026,295</t>
         </is>
       </c>
     </row>
@@ -4120,26 +4120,26 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>08/14/2021</t>
+          <t>08/18/2021</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>6–21–49–65–67</t>
+          <t>35–36–51–55–61</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E128" t="n">
         <v>2</v>
       </c>
       <c r="F128" t="n">
-        <v>4928</v>
+        <v>4753</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>$26,548</t>
+          <t>$1,024,428</t>
         </is>
       </c>
     </row>
@@ -4149,26 +4149,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>08/11/2021</t>
+          <t>08/14/2021</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>12–18–20–29–30</t>
+          <t>6–21–49–65–67</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F129" t="n">
-        <v>4238</v>
+        <v>4928</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>$27,758</t>
+          <t>$26,548</t>
         </is>
       </c>
     </row>
@@ -4178,26 +4178,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>08/07/2021</t>
+          <t>08/11/2021</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>7–24–36–54–60</t>
+          <t>12–18–20–29–30</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F130" t="n">
-        <v>4741</v>
+        <v>4238</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>$24,513</t>
+          <t>$27,758</t>
         </is>
       </c>
     </row>
@@ -4207,26 +4207,26 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>08/04/2021</t>
+          <t>08/07/2021</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>5–21–32–36–58</t>
+          <t>7–24–36–54–60</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E131" t="n">
         <v>2</v>
       </c>
       <c r="F131" t="n">
-        <v>3946</v>
+        <v>4741</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>$21,111</t>
+          <t>$24,513</t>
         </is>
       </c>
     </row>
@@ -4236,26 +4236,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>07/31/2021</t>
+          <t>08/04/2021</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>1–21–22–34–47</t>
+          <t>5–21–32–36–58</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E132" t="n">
         <v>2</v>
       </c>
       <c r="F132" t="n">
-        <v>4505</v>
+        <v>3946</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>$24,120</t>
+          <t>$21,111</t>
         </is>
       </c>
     </row>
@@ -4265,26 +4265,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>07/28/2021</t>
+          <t>07/31/2021</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>25–30–53–59–60</t>
+          <t>1–21–22–34–47</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F133" t="n">
-        <v>3889</v>
+        <v>4505</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>$73,912</t>
+          <t>$24,120</t>
         </is>
       </c>
     </row>
@@ -4294,26 +4294,26 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>07/24/2021</t>
+          <t>07/28/2021</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>1–4–11–59–67</t>
+          <t>25–30–53–59–60</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F134" t="n">
-        <v>4261</v>
+        <v>3889</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>$24,125</t>
+          <t>$73,912</t>
         </is>
       </c>
     </row>
@@ -4323,26 +4323,26 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>07/21/2021</t>
+          <t>07/24/2021</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>27–28–44–67–68</t>
+          <t>1–4–11–59–67</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E135" t="n">
         <v>2</v>
       </c>
       <c r="F135" t="n">
-        <v>3921</v>
+        <v>4261</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>$1,071,075</t>
+          <t>$24,125</t>
         </is>
       </c>
     </row>
@@ -4352,26 +4352,26 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>07/17/2021</t>
+          <t>07/21/2021</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>15–22–38–54–66</t>
+          <t>27–28–44–67–68</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E136" t="n">
         <v>2</v>
       </c>
       <c r="F136" t="n">
-        <v>4139</v>
+        <v>3921</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>$121,736</t>
+          <t>$1,071,075</t>
         </is>
       </c>
     </row>
@@ -4381,26 +4381,26 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>07/14/2021</t>
+          <t>07/17/2021</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>33–46–52–59–62</t>
+          <t>15–22–38–54–66</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E137" t="n">
         <v>2</v>
       </c>
       <c r="F137" t="n">
-        <v>3626</v>
+        <v>4139</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>$18,667</t>
+          <t>$121,736</t>
         </is>
       </c>
     </row>
@@ -4410,26 +4410,26 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>07/10/2021</t>
+          <t>07/14/2021</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>1–5–29–54–62</t>
+          <t>33–46–52–59–62</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E138" t="n">
         <v>2</v>
       </c>
       <c r="F138" t="n">
-        <v>3988</v>
+        <v>3626</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>$171,952</t>
+          <t>$18,667</t>
         </is>
       </c>
     </row>
@@ -4439,26 +4439,26 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>07/07/2021</t>
+          <t>07/10/2021</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>8–21–30–49–57</t>
+          <t>1–5–29–54–62</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E139" t="n">
         <v>2</v>
       </c>
       <c r="F139" t="n">
-        <v>3589</v>
+        <v>3988</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>$19,961</t>
+          <t>$171,952</t>
         </is>
       </c>
     </row>
@@ -4468,26 +4468,26 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>07/03/2021</t>
+          <t>07/07/2021</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>26–40–41–55–65</t>
+          <t>8–21–30–49–57</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E140" t="n">
         <v>2</v>
       </c>
       <c r="F140" t="n">
-        <v>4074</v>
+        <v>3589</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>$21,576</t>
+          <t>$19,961</t>
         </is>
       </c>
     </row>
@@ -4497,26 +4497,26 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>06/30/2021</t>
+          <t>07/03/2021</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>24–29–50–65–66</t>
+          <t>26–40–41–55–65</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E141" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F141" t="n">
-        <v>3195</v>
+        <v>4074</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>$73,597</t>
+          <t>$21,576</t>
         </is>
       </c>
     </row>
@@ -4526,26 +4526,26 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>06/26/2021</t>
+          <t>06/30/2021</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>8–31–39–43–60</t>
+          <t>24–29–50–65–66</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F142" t="n">
-        <v>3541</v>
+        <v>3195</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>$22,713</t>
+          <t>$73,597</t>
         </is>
       </c>
     </row>
@@ -4555,26 +4555,26 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>06/23/2021</t>
+          <t>06/26/2021</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>13–20–40–51–63</t>
+          <t>8–31–39–43–60</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E143" t="n">
         <v>3</v>
       </c>
       <c r="F143" t="n">
-        <v>2796</v>
+        <v>3541</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>$16,908</t>
+          <t>$22,713</t>
         </is>
       </c>
     </row>
@@ -4584,26 +4584,26 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>06/19/2021</t>
+          <t>06/23/2021</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>4–22–35–38–39</t>
+          <t>13–20–40–51–63</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F144" t="n">
-        <v>3396</v>
+        <v>2796</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>$18,109</t>
+          <t>$16,908</t>
         </is>
       </c>
     </row>
@@ -4613,26 +4613,26 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>06/16/2021</t>
+          <t>06/19/2021</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>19–29–34–44–50</t>
+          <t>4–22–35–38–39</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E145" t="n">
         <v>2</v>
       </c>
       <c r="F145" t="n">
-        <v>3102</v>
+        <v>3396</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>$15,857</t>
+          <t>$18,109</t>
         </is>
       </c>
     </row>
@@ -4642,26 +4642,26 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>06/12/2021</t>
+          <t>06/16/2021</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>8–25–34–38–41</t>
+          <t>19–29–34–44–50</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F146" t="n">
-        <v>3386</v>
+        <v>3102</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>$21,343</t>
+          <t>$15,857</t>
         </is>
       </c>
     </row>
@@ -4671,26 +4671,26 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>06/09/2021</t>
+          <t>06/12/2021</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>19–28–46–50–54</t>
+          <t>8–25–34–38–41</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F147" t="n">
-        <v>3205</v>
+        <v>3386</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>$17,283</t>
+          <t>$21,343</t>
         </is>
       </c>
     </row>
